--- a/research/traditional_assets/database/data/malawi/malawi_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_real_estate_operations_services.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1361520696285528</v>
+        <v>0.1360564175589242</v>
       </c>
       <c r="C2">
-        <v>29.33449484981884</v>
+        <v>29.0899938731326</v>
       </c>
       <c r="D2">
-        <v>27.17449484981884</v>
+        <v>27.2032938731326</v>
       </c>
       <c r="E2">
-        <v>-2.73</v>
+        <v>-2.4567</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2733</v>
       </c>
       <c r="G2">
         <v>2.16</v>
@@ -1576,28 +1576,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01374699</v>
       </c>
       <c r="N2">
-        <v>1.163333333333333</v>
+        <v>1.149586343333333</v>
       </c>
       <c r="O2">
-        <v>0.1163333333333333</v>
+        <v>0.1149586343333333</v>
       </c>
       <c r="P2">
-        <v>1.047</v>
+        <v>1.034627709</v>
       </c>
       <c r="Q2">
-        <v>1.101</v>
+        <v>1.088627709</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1361520696285528</v>
+        <v>0.1369734520797214</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.557605483217797</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>84.62458569718412</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1360564175589242</v>
+        <v>0.1359607654892956</v>
       </c>
       <c r="C3">
-        <v>29.0899938731326</v>
+        <v>28.84555400254209</v>
       </c>
       <c r="D3">
-        <v>27.2032938731326</v>
+        <v>27.23215400254209</v>
       </c>
       <c r="E3">
-        <v>-2.4567</v>
+        <v>-2.1834</v>
       </c>
       <c r="F3">
-        <v>0.2733</v>
+        <v>0.5466000000000001</v>
       </c>
       <c r="G3">
         <v>2.16</v>
@@ -1658,28 +1658,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M3">
-        <v>0.01374699</v>
+        <v>0.02749398</v>
       </c>
       <c r="N3">
-        <v>1.149586343333333</v>
+        <v>1.135839353333333</v>
       </c>
       <c r="O3">
-        <v>0.1149586343333333</v>
+        <v>0.1135839353333333</v>
       </c>
       <c r="P3">
-        <v>1.034627709</v>
+        <v>1.022255418</v>
       </c>
       <c r="Q3">
-        <v>1.088627709</v>
+        <v>1.076255418</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1369734520797214</v>
+        <v>0.1378115974380568</v>
       </c>
       <c r="T3">
-        <v>0.557605483217797</v>
+        <v>0.5627314758930847</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>84.62458569718412</v>
+        <v>42.31229284859206</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1359607654892956</v>
+        <v>0.1358651134196671</v>
       </c>
       <c r="C4">
-        <v>28.84555400254209</v>
+        <v>28.60117543273724</v>
       </c>
       <c r="D4">
-        <v>27.23215400254209</v>
+        <v>27.26107543273724</v>
       </c>
       <c r="E4">
-        <v>-2.1834</v>
+        <v>-1.9101</v>
       </c>
       <c r="F4">
-        <v>0.5466000000000001</v>
+        <v>0.8199000000000001</v>
       </c>
       <c r="G4">
         <v>2.16</v>
@@ -1740,28 +1740,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M4">
-        <v>0.02749398</v>
+        <v>0.04124097</v>
       </c>
       <c r="N4">
-        <v>1.135839353333333</v>
+        <v>1.122092363333333</v>
       </c>
       <c r="O4">
-        <v>0.1135839353333333</v>
+        <v>0.1122092363333333</v>
       </c>
       <c r="P4">
-        <v>1.022255418</v>
+        <v>1.009883127</v>
       </c>
       <c r="Q4">
-        <v>1.076255418</v>
+        <v>1.063883127</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1378115974380568</v>
+        <v>0.1386670241439867</v>
       </c>
       <c r="T4">
-        <v>0.5627314758930847</v>
+        <v>0.5679631591389969</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.31229284859206</v>
+        <v>28.20819523239471</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1358651134196671</v>
+        <v>0.1357694613500386</v>
       </c>
       <c r="C5">
-        <v>28.60117543273724</v>
+        <v>28.356858359236</v>
       </c>
       <c r="D5">
-        <v>27.26107543273724</v>
+        <v>27.290058359236</v>
       </c>
       <c r="E5">
-        <v>-1.9101</v>
+        <v>-1.6368</v>
       </c>
       <c r="F5">
-        <v>0.8199000000000001</v>
+        <v>1.0932</v>
       </c>
       <c r="G5">
         <v>2.16</v>
@@ -1822,28 +1822,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M5">
-        <v>0.04124097</v>
+        <v>0.05498796000000001</v>
       </c>
       <c r="N5">
-        <v>1.122092363333333</v>
+        <v>1.108345373333333</v>
       </c>
       <c r="O5">
-        <v>0.1122092363333333</v>
+        <v>0.1108345373333333</v>
       </c>
       <c r="P5">
-        <v>1.009883127</v>
+        <v>0.9975108359999999</v>
       </c>
       <c r="Q5">
-        <v>1.063883127</v>
+        <v>1.051510836</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1386670241439867</v>
+        <v>0.1395402722396235</v>
       </c>
       <c r="T5">
-        <v>0.5679631591389969</v>
+        <v>0.5733038357858656</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.20819523239471</v>
+        <v>21.15614642429603</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1357694613500386</v>
+        <v>0.13567380928041</v>
       </c>
       <c r="C6">
-        <v>28.356858359236</v>
+        <v>28.11260297838864</v>
       </c>
       <c r="D6">
-        <v>27.290058359236</v>
+        <v>27.31910297838863</v>
       </c>
       <c r="E6">
-        <v>-1.6368</v>
+        <v>-1.3635</v>
       </c>
       <c r="F6">
-        <v>1.0932</v>
+        <v>1.3665</v>
       </c>
       <c r="G6">
         <v>2.16</v>
@@ -1904,28 +1904,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M6">
-        <v>0.05498796000000001</v>
+        <v>0.06873495000000002</v>
       </c>
       <c r="N6">
-        <v>1.108345373333333</v>
+        <v>1.094598383333333</v>
       </c>
       <c r="O6">
-        <v>0.1108345373333333</v>
+        <v>0.1094598383333333</v>
       </c>
       <c r="P6">
-        <v>0.9975108359999999</v>
+        <v>0.9851385449999999</v>
       </c>
       <c r="Q6">
-        <v>1.051510836</v>
+        <v>1.039138545</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1395402722396235</v>
+        <v>0.1404319045056947</v>
       </c>
       <c r="T6">
-        <v>0.5733038357858656</v>
+        <v>0.5787569477305631</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.15614642429603</v>
+        <v>16.92491713943682</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.13567380928041</v>
+        <v>0.1355781572107815</v>
       </c>
       <c r="C7">
-        <v>28.11260297838864</v>
+        <v>27.86840948738216</v>
       </c>
       <c r="D7">
-        <v>27.31910297838863</v>
+        <v>27.34820948738216</v>
       </c>
       <c r="E7">
-        <v>-1.3635</v>
+        <v>-1.0902</v>
       </c>
       <c r="F7">
-        <v>1.3665</v>
+        <v>1.6398</v>
       </c>
       <c r="G7">
         <v>2.16</v>
@@ -1986,28 +1986,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M7">
-        <v>0.06873495000000002</v>
+        <v>0.08248194</v>
       </c>
       <c r="N7">
-        <v>1.094598383333333</v>
+        <v>1.080851393333333</v>
       </c>
       <c r="O7">
-        <v>0.1094598383333333</v>
+        <v>0.1080851393333333</v>
       </c>
       <c r="P7">
-        <v>0.9851385449999999</v>
+        <v>0.9727662539999999</v>
       </c>
       <c r="Q7">
-        <v>1.039138545</v>
+        <v>1.026766254</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1404319045056947</v>
+        <v>0.1413425076710441</v>
       </c>
       <c r="T7">
-        <v>0.5787569477305631</v>
+        <v>0.5843260833336585</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.92491713943682</v>
+        <v>14.10409761619735</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1355781572107815</v>
+        <v>0.1355770051411529</v>
       </c>
       <c r="C8">
-        <v>27.86840948738216</v>
+        <v>27.59546043517215</v>
       </c>
       <c r="D8">
-        <v>27.34820948738216</v>
+        <v>27.34856043517215</v>
       </c>
       <c r="E8">
-        <v>-1.0902</v>
+        <v>-0.8169</v>
       </c>
       <c r="F8">
-        <v>1.6398</v>
+        <v>1.9131</v>
       </c>
       <c r="G8">
         <v>2.16</v>
@@ -2068,45 +2068,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M8">
-        <v>0.08248194</v>
+        <v>0.09909858000000001</v>
       </c>
       <c r="N8">
-        <v>1.080851393333333</v>
+        <v>1.064234753333333</v>
       </c>
       <c r="O8">
-        <v>0.1080851393333333</v>
+        <v>0.1064234753333334</v>
       </c>
       <c r="P8">
-        <v>0.9727662539999999</v>
+        <v>0.9578112780000001</v>
       </c>
       <c r="Q8">
-        <v>1.026766254</v>
+        <v>1.011811278</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1413425076710441</v>
+        <v>0.1422726937001644</v>
       </c>
       <c r="T8">
-        <v>0.5843260833336585</v>
+        <v>0.5900149852938096</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.10409761619735</v>
+        <v>11.73915240090558</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1355770051411529</v>
+        <v>0.1354948530715244</v>
       </c>
       <c r="C9">
-        <v>27.59546043517214</v>
+        <v>27.34720915050166</v>
       </c>
       <c r="D9">
-        <v>27.34856043517214</v>
+        <v>27.37360915050165</v>
       </c>
       <c r="E9">
-        <v>-0.8168999999999997</v>
+        <v>-0.5435999999999996</v>
       </c>
       <c r="F9">
-        <v>1.9131</v>
+        <v>2.1864</v>
       </c>
       <c r="G9">
         <v>2.16</v>
@@ -2150,28 +2150,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M9">
-        <v>0.09909858000000001</v>
+        <v>0.11325552</v>
       </c>
       <c r="N9">
-        <v>1.064234753333333</v>
+        <v>1.050077813333333</v>
       </c>
       <c r="O9">
-        <v>0.1064234753333334</v>
+        <v>0.1050077813333333</v>
       </c>
       <c r="P9">
-        <v>0.9578112780000001</v>
+        <v>0.9450700319999999</v>
       </c>
       <c r="Q9">
-        <v>1.011811278</v>
+        <v>0.999070032</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1422726937001644</v>
+        <v>0.1432231011647004</v>
       </c>
       <c r="T9">
-        <v>0.5900149852938097</v>
+        <v>0.5958275590357032</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.73915240090558</v>
+        <v>10.27175835079238</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1354948530715244</v>
+        <v>0.1355504010018958</v>
       </c>
       <c r="C10">
-        <v>27.34720915050166</v>
+        <v>27.05696719460917</v>
       </c>
       <c r="D10">
-        <v>27.37360915050165</v>
+        <v>27.35666719460917</v>
       </c>
       <c r="E10">
-        <v>-0.5435999999999996</v>
+        <v>-0.2702999999999998</v>
       </c>
       <c r="F10">
-        <v>2.1864</v>
+        <v>2.4597</v>
       </c>
       <c r="G10">
         <v>2.16</v>
@@ -2232,45 +2232,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M10">
-        <v>0.11325552</v>
+        <v>0.13159395</v>
       </c>
       <c r="N10">
-        <v>1.050077813333333</v>
+        <v>1.031739383333333</v>
       </c>
       <c r="O10">
-        <v>0.1050077813333333</v>
+        <v>0.1031739383333333</v>
       </c>
       <c r="P10">
-        <v>0.9450700319999999</v>
+        <v>0.9285654449999999</v>
       </c>
       <c r="Q10">
-        <v>0.999070032</v>
+        <v>0.982565445</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1432231011647004</v>
+        <v>0.14419439670538</v>
       </c>
       <c r="T10">
-        <v>0.5958275590357032</v>
+        <v>0.6017678816510449</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.27175835079238</v>
+        <v>8.840325359435848</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1355504010018958</v>
+        <v>0.1354835489322673</v>
       </c>
       <c r="C11">
-        <v>27.05696719460917</v>
+        <v>26.80405944984295</v>
       </c>
       <c r="D11">
-        <v>27.35666719460917</v>
+        <v>27.37705944984295</v>
       </c>
       <c r="E11">
-        <v>-0.2702999999999998</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="F11">
-        <v>2.4597</v>
+        <v>2.733</v>
       </c>
       <c r="G11">
         <v>2.16</v>
@@ -2314,28 +2314,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M11">
-        <v>0.13159395</v>
+        <v>0.1462155</v>
       </c>
       <c r="N11">
-        <v>1.031739383333333</v>
+        <v>1.017117833333333</v>
       </c>
       <c r="O11">
-        <v>0.1031739383333333</v>
+        <v>0.1017117833333333</v>
       </c>
       <c r="P11">
-        <v>0.9285654449999999</v>
+        <v>0.91540605</v>
       </c>
       <c r="Q11">
-        <v>0.982565445</v>
+        <v>0.96940605</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.14419439670538</v>
+        <v>0.1451872765914081</v>
       </c>
       <c r="T11">
-        <v>0.6017678816510449</v>
+        <v>0.6078402114356166</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.840325359435848</v>
+        <v>7.956292823492265</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1354835489322673</v>
+        <v>0.1354958968626387</v>
       </c>
       <c r="C12">
-        <v>26.80405944984295</v>
+        <v>26.5269906038234</v>
       </c>
       <c r="D12">
-        <v>27.37705944984295</v>
+        <v>27.3732906038234</v>
       </c>
       <c r="E12">
-        <v>0.003000000000000558</v>
+        <v>0.2763000000000004</v>
       </c>
       <c r="F12">
-        <v>2.733000000000001</v>
+        <v>3.0063</v>
       </c>
       <c r="G12">
         <v>2.16</v>
@@ -2396,45 +2396,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M12">
-        <v>0.1462155</v>
+        <v>0.16324209</v>
       </c>
       <c r="N12">
-        <v>1.017117833333333</v>
+        <v>1.000091243333333</v>
       </c>
       <c r="O12">
-        <v>0.1017117833333333</v>
+        <v>0.1000091243333333</v>
       </c>
       <c r="P12">
-        <v>0.91540605</v>
+        <v>0.900082119</v>
       </c>
       <c r="Q12">
-        <v>0.96940605</v>
+        <v>0.9540821190000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1451872765914081</v>
+        <v>0.1462024683849873</v>
       </c>
       <c r="T12">
-        <v>0.6078402114356166</v>
+        <v>0.6140489980692796</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.956292823492264</v>
+        <v>7.126430036109762</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1354958968626387</v>
+        <v>0.1354362447930101</v>
       </c>
       <c r="C13">
-        <v>26.5269906038234</v>
+        <v>26.27190726875434</v>
       </c>
       <c r="D13">
-        <v>27.3732906038234</v>
+        <v>27.39150726875434</v>
       </c>
       <c r="E13">
-        <v>0.2763000000000004</v>
+        <v>0.5496000000000003</v>
       </c>
       <c r="F13">
-        <v>3.0063</v>
+        <v>3.2796</v>
       </c>
       <c r="G13">
         <v>2.16</v>
@@ -2478,28 +2478,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M13">
-        <v>0.16324209</v>
+        <v>0.17808228</v>
       </c>
       <c r="N13">
-        <v>1.000091243333333</v>
+        <v>0.9852510533333333</v>
       </c>
       <c r="O13">
-        <v>0.1000091243333333</v>
+        <v>0.09852510533333333</v>
       </c>
       <c r="P13">
-        <v>0.900082119</v>
+        <v>0.8867259479999999</v>
       </c>
       <c r="Q13">
-        <v>0.9540821190000001</v>
+        <v>0.940725948</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1462024683849873</v>
+        <v>0.1472407327193297</v>
       </c>
       <c r="T13">
-        <v>0.6140489980692796</v>
+        <v>0.6203988934900715</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.126430036109762</v>
+        <v>6.53256086643395</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1354362447930101</v>
+        <v>0.1354935927233816</v>
       </c>
       <c r="C14">
-        <v>26.27190726875434</v>
+        <v>25.98109379645468</v>
       </c>
       <c r="D14">
-        <v>27.39150726875434</v>
+        <v>27.37399379645468</v>
       </c>
       <c r="E14">
-        <v>0.5496000000000003</v>
+        <v>0.8229000000000002</v>
       </c>
       <c r="F14">
-        <v>3.2796</v>
+        <v>3.5529</v>
       </c>
       <c r="G14">
         <v>2.16</v>
@@ -2560,45 +2560,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M14">
-        <v>0.17808228</v>
+        <v>0.19647537</v>
       </c>
       <c r="N14">
-        <v>0.9852510533333333</v>
+        <v>0.9668579633333333</v>
       </c>
       <c r="O14">
-        <v>0.09852510533333333</v>
+        <v>0.09668579633333334</v>
       </c>
       <c r="P14">
-        <v>0.8867259479999999</v>
+        <v>0.870172167</v>
       </c>
       <c r="Q14">
-        <v>0.940725948</v>
+        <v>0.924172167</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1472407327193297</v>
+        <v>0.1483028651992892</v>
       </c>
       <c r="T14">
-        <v>0.6203988934900715</v>
+        <v>0.6268947635182377</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.53256086643395</v>
+        <v>5.921013577087719</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1354935927233816</v>
+        <v>0.135442940653753</v>
       </c>
       <c r="C15">
-        <v>25.98109379645468</v>
+        <v>25.72326126583575</v>
       </c>
       <c r="D15">
-        <v>27.37399379645468</v>
+        <v>27.38946126583575</v>
       </c>
       <c r="E15">
-        <v>0.8229000000000002</v>
+        <v>1.096200000000001</v>
       </c>
       <c r="F15">
-        <v>3.5529</v>
+        <v>3.8262</v>
       </c>
       <c r="G15">
         <v>2.16</v>
@@ -2642,28 +2642,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M15">
-        <v>0.19647537</v>
+        <v>0.21158886</v>
       </c>
       <c r="N15">
-        <v>0.9668579633333333</v>
+        <v>0.9517444733333333</v>
       </c>
       <c r="O15">
-        <v>0.09668579633333334</v>
+        <v>0.09517444733333334</v>
       </c>
       <c r="P15">
-        <v>0.870172167</v>
+        <v>0.856570026</v>
       </c>
       <c r="Q15">
-        <v>0.924172167</v>
+        <v>0.910570026</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1483028651992892</v>
+        <v>0.1493896984345965</v>
       </c>
       <c r="T15">
-        <v>0.6268947635182377</v>
+        <v>0.6335417002912451</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.921013577087719</v>
+        <v>5.498084035867167</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.135442940653753</v>
+        <v>0.1353922885841245</v>
       </c>
       <c r="C16">
-        <v>25.72326126583575</v>
+        <v>25.46544622465362</v>
       </c>
       <c r="D16">
-        <v>27.38946126583575</v>
+        <v>27.40494622465362</v>
       </c>
       <c r="E16">
-        <v>1.096200000000001</v>
+        <v>1.369500000000001</v>
       </c>
       <c r="F16">
-        <v>3.8262</v>
+        <v>4.099500000000001</v>
       </c>
       <c r="G16">
         <v>2.16</v>
@@ -2724,28 +2724,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M16">
-        <v>0.21158886</v>
+        <v>0.2267023500000001</v>
       </c>
       <c r="N16">
-        <v>0.9517444733333333</v>
+        <v>0.9366309833333333</v>
       </c>
       <c r="O16">
-        <v>0.09517444733333334</v>
+        <v>0.09366309833333333</v>
       </c>
       <c r="P16">
-        <v>0.856570026</v>
+        <v>0.842967885</v>
       </c>
       <c r="Q16">
-        <v>0.910570026</v>
+        <v>0.896967885</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1493896984345965</v>
+        <v>0.1505021042166171</v>
       </c>
       <c r="T16">
-        <v>0.6335417002912451</v>
+        <v>0.6403450355765586</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.498084035867167</v>
+        <v>5.13154510014269</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1353922885841245</v>
+        <v>0.1353416365144959</v>
       </c>
       <c r="C17">
-        <v>25.46544622465362</v>
+        <v>25.20764870258872</v>
       </c>
       <c r="D17">
-        <v>27.40494622465362</v>
+        <v>27.42044870258872</v>
       </c>
       <c r="E17">
-        <v>1.3695</v>
+        <v>1.642800000000001</v>
       </c>
       <c r="F17">
-        <v>4.0995</v>
+        <v>4.372800000000001</v>
       </c>
       <c r="G17">
         <v>2.16</v>
@@ -2806,28 +2806,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M17">
-        <v>0.22670235</v>
+        <v>0.2418158400000001</v>
       </c>
       <c r="N17">
-        <v>0.9366309833333333</v>
+        <v>0.9215174933333332</v>
       </c>
       <c r="O17">
-        <v>0.09366309833333333</v>
+        <v>0.09215174933333332</v>
       </c>
       <c r="P17">
-        <v>0.842967885</v>
+        <v>0.8293657439999998</v>
       </c>
       <c r="Q17">
-        <v>0.896967885</v>
+        <v>0.8833657439999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1505021042166171</v>
+        <v>0.1516409958505904</v>
       </c>
       <c r="T17">
-        <v>0.6403450355765586</v>
+        <v>0.647310355035332</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.131545100142691</v>
+        <v>4.810823531383772</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1353416365144959</v>
+        <v>0.1352909844448674</v>
       </c>
       <c r="C18">
-        <v>25.20764870258872</v>
+        <v>24.94986872938858</v>
       </c>
       <c r="D18">
-        <v>27.42044870258872</v>
+        <v>27.43596872938858</v>
       </c>
       <c r="E18">
-        <v>1.642800000000001</v>
+        <v>1.916100000000001</v>
       </c>
       <c r="F18">
-        <v>4.372800000000001</v>
+        <v>4.646100000000001</v>
       </c>
       <c r="G18">
         <v>2.16</v>
@@ -2888,28 +2888,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M18">
-        <v>0.2418158400000001</v>
+        <v>0.2569293300000001</v>
       </c>
       <c r="N18">
-        <v>0.9215174933333332</v>
+        <v>0.9064040033333333</v>
       </c>
       <c r="O18">
-        <v>0.09215174933333332</v>
+        <v>0.09064040033333333</v>
       </c>
       <c r="P18">
-        <v>0.8293657439999998</v>
+        <v>0.8157636029999999</v>
       </c>
       <c r="Q18">
-        <v>0.8833657439999999</v>
+        <v>0.869763603</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1516409958505904</v>
+        <v>0.1528073306564667</v>
       </c>
       <c r="T18">
-        <v>0.647310355035332</v>
+        <v>0.6544435135172082</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.810823531383772</v>
+        <v>4.527833911890609</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1352909844448674</v>
+        <v>0.1356453323752388</v>
       </c>
       <c r="C19">
-        <v>24.94986872938858</v>
+        <v>24.56836189793749</v>
       </c>
       <c r="D19">
-        <v>27.43596872938858</v>
+        <v>27.32776189793749</v>
       </c>
       <c r="E19">
-        <v>1.916100000000001</v>
+        <v>2.189400000000001</v>
       </c>
       <c r="F19">
-        <v>4.646100000000001</v>
+        <v>4.919400000000001</v>
       </c>
       <c r="G19">
         <v>2.16</v>
@@ -2970,45 +2970,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M19">
-        <v>0.2569293300000001</v>
+        <v>0.2843413200000001</v>
       </c>
       <c r="N19">
-        <v>0.9064040033333333</v>
+        <v>0.8789920133333332</v>
       </c>
       <c r="O19">
-        <v>0.09064040033333333</v>
+        <v>0.08789920133333333</v>
       </c>
       <c r="P19">
-        <v>0.8157636029999999</v>
+        <v>0.7910928119999999</v>
       </c>
       <c r="Q19">
-        <v>0.869763603</v>
+        <v>0.845092812</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1528073306564667</v>
+        <v>0.1540021126527303</v>
       </c>
       <c r="T19">
-        <v>0.6544435135172082</v>
+        <v>0.6617506514742522</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.527833911890609</v>
+        <v>4.091327047835794</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1356453323752388</v>
+        <v>0.1362156803056103</v>
       </c>
       <c r="C20">
-        <v>24.56836189793748</v>
+        <v>24.12267661711572</v>
       </c>
       <c r="D20">
-        <v>27.32776189793748</v>
+        <v>27.15537661711572</v>
       </c>
       <c r="E20">
-        <v>2.1894</v>
+        <v>2.4627</v>
       </c>
       <c r="F20">
-        <v>4.9194</v>
+        <v>5.1927</v>
       </c>
       <c r="G20">
         <v>2.16</v>
@@ -3052,45 +3052,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M20">
-        <v>0.2843413200000001</v>
+        <v>0.31831251</v>
       </c>
       <c r="N20">
-        <v>0.8789920133333333</v>
+        <v>0.8450208233333333</v>
       </c>
       <c r="O20">
-        <v>0.08789920133333334</v>
+        <v>0.08450208233333334</v>
       </c>
       <c r="P20">
-        <v>0.791092812</v>
+        <v>0.7605187409999999</v>
       </c>
       <c r="Q20">
-        <v>0.8450928120000001</v>
+        <v>0.814518741</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1540021126527303</v>
+        <v>0.155226395439025</v>
       </c>
       <c r="T20">
-        <v>0.6617506514742522</v>
+        <v>0.6692382125907294</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.091327047835795</v>
+        <v>3.654689328211867</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1362156803056103</v>
+        <v>0.1367230282359817</v>
       </c>
       <c r="C21">
-        <v>24.12267661711572</v>
+        <v>23.6978503823164</v>
       </c>
       <c r="D21">
-        <v>27.15537661711572</v>
+        <v>27.0038503823164</v>
       </c>
       <c r="E21">
-        <v>2.4627</v>
+        <v>2.736000000000001</v>
       </c>
       <c r="F21">
-        <v>5.1927</v>
+        <v>5.466000000000001</v>
       </c>
       <c r="G21">
         <v>2.16</v>
@@ -3134,45 +3134,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M21">
-        <v>0.31831251</v>
+        <v>0.3503706000000001</v>
       </c>
       <c r="N21">
-        <v>0.8450208233333333</v>
+        <v>0.8129627333333332</v>
       </c>
       <c r="O21">
-        <v>0.08450208233333334</v>
+        <v>0.08129627333333334</v>
       </c>
       <c r="P21">
-        <v>0.7605187409999999</v>
+        <v>0.7316664599999999</v>
       </c>
       <c r="Q21">
-        <v>0.814518741</v>
+        <v>0.78566646</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.155226395439025</v>
+        <v>0.1564812852949772</v>
       </c>
       <c r="T21">
-        <v>0.6692382125907294</v>
+        <v>0.6769129627351185</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.654689328211867</v>
+        <v>3.320293806995601</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1367230282359817</v>
+        <v>0.1367515761663532</v>
       </c>
       <c r="C22">
-        <v>23.6978503823164</v>
+        <v>23.41607439901882</v>
       </c>
       <c r="D22">
-        <v>27.0038503823164</v>
+        <v>26.99537439901882</v>
       </c>
       <c r="E22">
-        <v>2.736000000000001</v>
+        <v>3.009300000000001</v>
       </c>
       <c r="F22">
-        <v>5.466000000000001</v>
+        <v>5.739300000000001</v>
       </c>
       <c r="G22">
         <v>2.16</v>
@@ -3216,28 +3216,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M22">
-        <v>0.3503706000000001</v>
+        <v>0.3678891300000001</v>
       </c>
       <c r="N22">
-        <v>0.8129627333333332</v>
+        <v>0.7954442033333333</v>
       </c>
       <c r="O22">
-        <v>0.08129627333333334</v>
+        <v>0.07954442033333334</v>
       </c>
       <c r="P22">
-        <v>0.7316664599999999</v>
+        <v>0.715899783</v>
       </c>
       <c r="Q22">
-        <v>0.78566646</v>
+        <v>0.7698997830000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1564812852949772</v>
+        <v>0.1577679445143711</v>
       </c>
       <c r="T22">
-        <v>0.6769129627351185</v>
+        <v>0.6847820103515174</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.320293806995601</v>
+        <v>3.162184578091049</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1367515761663532</v>
+        <v>0.1367801240967246</v>
       </c>
       <c r="C23">
-        <v>23.41607439901882</v>
+        <v>23.13430373494415</v>
       </c>
       <c r="D23">
-        <v>26.99537439901882</v>
+        <v>26.98690373494416</v>
       </c>
       <c r="E23">
-        <v>3.0093</v>
+        <v>3.282600000000001</v>
       </c>
       <c r="F23">
-        <v>5.7393</v>
+        <v>6.012600000000001</v>
       </c>
       <c r="G23">
         <v>2.16</v>
@@ -3298,28 +3298,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M23">
-        <v>0.36788913</v>
+        <v>0.3854076600000001</v>
       </c>
       <c r="N23">
-        <v>0.7954442033333333</v>
+        <v>0.7779256733333333</v>
       </c>
       <c r="O23">
-        <v>0.07954442033333334</v>
+        <v>0.07779256733333334</v>
       </c>
       <c r="P23">
-        <v>0.715899783</v>
+        <v>0.700133106</v>
       </c>
       <c r="Q23">
-        <v>0.7698997830000001</v>
+        <v>0.7541331060000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1577679445143711</v>
+        <v>0.1590875949958008</v>
       </c>
       <c r="T23">
-        <v>0.6847820103515174</v>
+        <v>0.6928528284196189</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.16218457809105</v>
+        <v>3.018448915450547</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1367801240967246</v>
+        <v>0.1384232720270961</v>
       </c>
       <c r="C24">
-        <v>23.13430373494415</v>
+        <v>22.38225283305165</v>
       </c>
       <c r="D24">
-        <v>26.98690373494416</v>
+        <v>26.50815283305165</v>
       </c>
       <c r="E24">
-        <v>3.282600000000001</v>
+        <v>3.555900000000001</v>
       </c>
       <c r="F24">
-        <v>6.012600000000001</v>
+        <v>6.285900000000001</v>
       </c>
       <c r="G24">
         <v>2.16</v>
@@ -3380,45 +3380,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M24">
-        <v>0.3854076600000001</v>
+        <v>0.4519562100000001</v>
       </c>
       <c r="N24">
-        <v>0.7779256733333333</v>
+        <v>0.7113771233333332</v>
       </c>
       <c r="O24">
-        <v>0.07779256733333334</v>
+        <v>0.07113771233333332</v>
       </c>
       <c r="P24">
-        <v>0.700133106</v>
+        <v>0.6402394109999999</v>
       </c>
       <c r="Q24">
-        <v>0.7541331060000001</v>
+        <v>0.694239411</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1590875949958008</v>
+        <v>0.1604415221131118</v>
       </c>
       <c r="T24">
-        <v>0.6928528284196189</v>
+        <v>0.7011332781258529</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.018448915450547</v>
+        <v>2.573995682752834</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1384232720270961</v>
+        <v>0.1393644199574675</v>
       </c>
       <c r="C25">
-        <v>22.38225283305165</v>
+        <v>21.84231201821908</v>
       </c>
       <c r="D25">
-        <v>26.50815283305165</v>
+        <v>26.24151201821908</v>
       </c>
       <c r="E25">
-        <v>3.555900000000001</v>
+        <v>3.829200000000001</v>
       </c>
       <c r="F25">
-        <v>6.285900000000001</v>
+        <v>6.559200000000001</v>
       </c>
       <c r="G25">
         <v>2.16</v>
@@ -3462,45 +3462,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M25">
-        <v>0.4519562100000001</v>
+        <v>0.4971873600000001</v>
       </c>
       <c r="N25">
-        <v>0.7113771233333332</v>
+        <v>0.6661459733333333</v>
       </c>
       <c r="O25">
-        <v>0.07113771233333332</v>
+        <v>0.06661459733333333</v>
       </c>
       <c r="P25">
-        <v>0.6402394109999999</v>
+        <v>0.5995313759999999</v>
       </c>
       <c r="Q25">
-        <v>0.694239411</v>
+        <v>0.653531376</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1604415221131118</v>
+        <v>0.1618310788914046</v>
       </c>
       <c r="T25">
-        <v>0.7011332781258529</v>
+        <v>0.7096316344033036</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.573995682752834</v>
+        <v>2.339828859151474</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1393644199574675</v>
+        <v>0.139498267887839</v>
       </c>
       <c r="C26">
-        <v>21.84231201821908</v>
+        <v>21.53152603098972</v>
       </c>
       <c r="D26">
-        <v>26.24151201821908</v>
+        <v>26.20402603098972</v>
       </c>
       <c r="E26">
-        <v>3.829200000000001</v>
+        <v>4.102500000000001</v>
       </c>
       <c r="F26">
-        <v>6.559200000000001</v>
+        <v>6.8325</v>
       </c>
       <c r="G26">
         <v>2.16</v>
@@ -3544,28 +3544,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M26">
-        <v>0.4971873600000001</v>
+        <v>0.5179035000000001</v>
       </c>
       <c r="N26">
-        <v>0.6661459733333333</v>
+        <v>0.6454298333333333</v>
       </c>
       <c r="O26">
-        <v>0.06661459733333333</v>
+        <v>0.06454298333333333</v>
       </c>
       <c r="P26">
-        <v>0.5995313759999999</v>
+        <v>0.58088685</v>
       </c>
       <c r="Q26">
-        <v>0.653531376</v>
+        <v>0.63488685</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1618310788914046</v>
+        <v>0.1632576905171186</v>
       </c>
       <c r="T26">
-        <v>0.7096316344033036</v>
+        <v>0.7183566135148196</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.339828859151474</v>
+        <v>2.246235704785415</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.139498267887839</v>
+        <v>0.1396321158182104</v>
       </c>
       <c r="C27">
-        <v>21.53152603098972</v>
+        <v>21.22084698841925</v>
       </c>
       <c r="D27">
-        <v>26.20402603098972</v>
+        <v>26.16664698841925</v>
       </c>
       <c r="E27">
-        <v>4.102500000000001</v>
+        <v>4.3758</v>
       </c>
       <c r="F27">
-        <v>6.8325</v>
+        <v>7.1058</v>
       </c>
       <c r="G27">
         <v>2.16</v>
@@ -3626,28 +3626,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M27">
-        <v>0.5179035000000001</v>
+        <v>0.5386196400000001</v>
       </c>
       <c r="N27">
-        <v>0.6454298333333333</v>
+        <v>0.6247136933333333</v>
       </c>
       <c r="O27">
-        <v>0.06454298333333333</v>
+        <v>0.06247136933333333</v>
       </c>
       <c r="P27">
-        <v>0.58088685</v>
+        <v>0.562242324</v>
       </c>
       <c r="Q27">
-        <v>0.63488685</v>
+        <v>0.616242324</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1632576905171186</v>
+        <v>0.1647228592137978</v>
       </c>
       <c r="T27">
-        <v>0.7183566135148196</v>
+        <v>0.7273174028725928</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.246235704785415</v>
+        <v>2.15984202383213</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1396321158182104</v>
+        <v>0.1397659637485819</v>
       </c>
       <c r="C28">
-        <v>21.22084698841925</v>
+        <v>20.91027443350211</v>
       </c>
       <c r="D28">
-        <v>26.16664698841925</v>
+        <v>26.12937443350211</v>
       </c>
       <c r="E28">
-        <v>4.3758</v>
+        <v>4.649100000000001</v>
       </c>
       <c r="F28">
-        <v>7.1058</v>
+        <v>7.379100000000001</v>
       </c>
       <c r="G28">
         <v>2.16</v>
@@ -3708,28 +3708,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M28">
-        <v>0.5386196400000001</v>
+        <v>0.5593357800000002</v>
       </c>
       <c r="N28">
-        <v>0.6247136933333333</v>
+        <v>0.6039975533333332</v>
       </c>
       <c r="O28">
-        <v>0.06247136933333333</v>
+        <v>0.06039975533333332</v>
       </c>
       <c r="P28">
-        <v>0.562242324</v>
+        <v>0.5435977979999999</v>
       </c>
       <c r="Q28">
-        <v>0.616242324</v>
+        <v>0.5975977979999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1647228592137978</v>
+        <v>0.1662281695186053</v>
       </c>
       <c r="T28">
-        <v>0.7273174028725928</v>
+        <v>0.7365236933086613</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.15984202383213</v>
+        <v>2.07984787480131</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1397659637485819</v>
+        <v>0.1398998116789533</v>
       </c>
       <c r="C29">
-        <v>20.91027443350211</v>
+        <v>20.599807911833</v>
       </c>
       <c r="D29">
-        <v>26.12937443350211</v>
+        <v>26.092207911833</v>
       </c>
       <c r="E29">
-        <v>4.649100000000001</v>
+        <v>4.922400000000001</v>
       </c>
       <c r="F29">
-        <v>7.379100000000001</v>
+        <v>7.652400000000001</v>
       </c>
       <c r="G29">
         <v>2.16</v>
@@ -3790,28 +3790,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M29">
-        <v>0.5593357800000002</v>
+        <v>0.5800519200000002</v>
       </c>
       <c r="N29">
-        <v>0.6039975533333332</v>
+        <v>0.5832814133333332</v>
       </c>
       <c r="O29">
-        <v>0.06039975533333332</v>
+        <v>0.05832814133333332</v>
       </c>
       <c r="P29">
-        <v>0.5435977979999999</v>
+        <v>0.5249532719999999</v>
       </c>
       <c r="Q29">
-        <v>0.5975977979999999</v>
+        <v>0.5789532719999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1662281695186053</v>
+        <v>0.1677752939985463</v>
       </c>
       <c r="T29">
-        <v>0.7365236933086613</v>
+        <v>0.7459857140346204</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.07984787480131</v>
+        <v>2.005567593558406</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1398998116789533</v>
+        <v>0.1437398596093248</v>
       </c>
       <c r="C30">
-        <v>20.599807911833</v>
+        <v>19.3034787856904</v>
       </c>
       <c r="D30">
-        <v>26.092207911833</v>
+        <v>25.0691787856904</v>
       </c>
       <c r="E30">
-        <v>4.922400000000001</v>
+        <v>5.195700000000002</v>
       </c>
       <c r="F30">
-        <v>7.652400000000001</v>
+        <v>7.925700000000002</v>
       </c>
       <c r="G30">
         <v>2.16</v>
@@ -3872,45 +3872,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M30">
-        <v>0.5800519200000002</v>
+        <v>0.7133130000000001</v>
       </c>
       <c r="N30">
-        <v>0.5832814133333332</v>
+        <v>0.4500203333333332</v>
       </c>
       <c r="O30">
-        <v>0.05832814133333332</v>
+        <v>0.04500203333333333</v>
       </c>
       <c r="P30">
-        <v>0.5249532719999999</v>
+        <v>0.4050182999999999</v>
       </c>
       <c r="Q30">
-        <v>0.5789532719999999</v>
+        <v>0.4590183</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1677752939985463</v>
+        <v>0.1693659994497532</v>
       </c>
       <c r="T30">
-        <v>0.7459857140346204</v>
+        <v>0.7557142705556771</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.005567593558406</v>
+        <v>1.630887609413165</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1437398596093248</v>
+        <v>0.1440015075396962</v>
       </c>
       <c r="C31">
-        <v>19.30347878569041</v>
+        <v>18.96338450819181</v>
       </c>
       <c r="D31">
-        <v>25.0691787856904</v>
+        <v>25.00238450819181</v>
       </c>
       <c r="E31">
-        <v>5.1957</v>
+        <v>5.468999999999999</v>
       </c>
       <c r="F31">
-        <v>7.9257</v>
+        <v>8.199</v>
       </c>
       <c r="G31">
         <v>2.16</v>
@@ -3954,28 +3954,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M31">
-        <v>0.713313</v>
+        <v>0.73791</v>
       </c>
       <c r="N31">
-        <v>0.4500203333333334</v>
+        <v>0.4254233333333334</v>
       </c>
       <c r="O31">
-        <v>0.04500203333333334</v>
+        <v>0.04254233333333334</v>
       </c>
       <c r="P31">
-        <v>0.4050183</v>
+        <v>0.382881</v>
       </c>
       <c r="Q31">
-        <v>0.4590183</v>
+        <v>0.4368810000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1693659994497532</v>
+        <v>0.1710021536281374</v>
       </c>
       <c r="T31">
-        <v>0.755714270555677</v>
+        <v>0.765720785834478</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.630887609413166</v>
+        <v>1.576524689099394</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1440015075396962</v>
+        <v>0.1442631554700677</v>
       </c>
       <c r="C32">
-        <v>18.96338450819181</v>
+        <v>18.62364521798534</v>
       </c>
       <c r="D32">
-        <v>25.00238450819181</v>
+        <v>24.93594521798534</v>
       </c>
       <c r="E32">
-        <v>5.468999999999999</v>
+        <v>5.7423</v>
       </c>
       <c r="F32">
-        <v>8.199</v>
+        <v>8.472300000000001</v>
       </c>
       <c r="G32">
         <v>2.16</v>
@@ -4036,28 +4036,28 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M32">
-        <v>0.73791</v>
+        <v>0.762507</v>
       </c>
       <c r="N32">
-        <v>0.4254233333333334</v>
+        <v>0.4008263333333333</v>
       </c>
       <c r="O32">
-        <v>0.04254233333333334</v>
+        <v>0.04008263333333333</v>
       </c>
       <c r="P32">
-        <v>0.382881</v>
+        <v>0.3607436999999999</v>
       </c>
       <c r="Q32">
-        <v>0.4368810000000001</v>
+        <v>0.4147437</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1710021536281374</v>
+        <v>0.1726857325653154</v>
       </c>
       <c r="T32">
-        <v>0.765720785834478</v>
+        <v>0.7760173450344038</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.576524689099394</v>
+        <v>1.525669053967155</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1442631554700677</v>
+        <v>0.1615956019809427</v>
       </c>
       <c r="C33">
-        <v>18.62364521798534</v>
+        <v>14.61789830899159</v>
       </c>
       <c r="D33">
-        <v>24.93594521798534</v>
+        <v>21.20349830899159</v>
       </c>
       <c r="E33">
-        <v>5.7423</v>
+        <v>6.015600000000001</v>
       </c>
       <c r="F33">
-        <v>8.472300000000001</v>
+        <v>8.745600000000001</v>
       </c>
       <c r="G33">
         <v>2.16</v>
@@ -4118,45 +4118,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M33">
-        <v>0.762507</v>
+        <v>1.28385408</v>
       </c>
       <c r="N33">
-        <v>0.4008263333333333</v>
+        <v>-0.1205207466666669</v>
       </c>
       <c r="O33">
-        <v>0.04008263333333333</v>
+        <v>-0.01205207466666669</v>
       </c>
       <c r="P33">
-        <v>0.3607436999999999</v>
+        <v>-0.1084686720000002</v>
       </c>
       <c r="Q33">
-        <v>0.4147437</v>
+        <v>-0.05446867200000016</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1726857325653154</v>
+        <v>0.1748179685904574</v>
       </c>
       <c r="T33">
-        <v>0.7760173450344038</v>
+        <v>0.7890578351333646</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1</v>
+        <v>0.0906125821817175</v>
       </c>
       <c r="W33">
-        <v>0.081</v>
+        <v>0.1334980729357239</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.525669053967155</v>
+        <v>0.906125821817175</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1615956019809427</v>
+        <v>0.1626056019809427</v>
       </c>
       <c r="C34">
-        <v>14.61789830899159</v>
+        <v>14.16125493394031</v>
       </c>
       <c r="D34">
-        <v>21.20349830899159</v>
+        <v>21.02015493394031</v>
       </c>
       <c r="E34">
-        <v>6.015600000000001</v>
+        <v>6.2889</v>
       </c>
       <c r="F34">
-        <v>8.745600000000001</v>
+        <v>9.0189</v>
       </c>
       <c r="G34">
         <v>2.16</v>
@@ -4200,37 +4200,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M34">
-        <v>1.28385408</v>
+        <v>1.32397452</v>
       </c>
       <c r="N34">
-        <v>-0.1205207466666669</v>
+        <v>-0.1606411866666668</v>
       </c>
       <c r="O34">
-        <v>-0.01205207466666669</v>
+        <v>-0.01606411866666668</v>
       </c>
       <c r="P34">
-        <v>-0.1084686720000002</v>
+        <v>-0.1445770680000001</v>
       </c>
       <c r="Q34">
-        <v>-0.05446867200000016</v>
+        <v>-0.09057706800000009</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1748179685904574</v>
+        <v>0.176743609912703</v>
       </c>
       <c r="T34">
-        <v>0.7890578351333646</v>
+        <v>0.8008348177472954</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.0906125821817175</v>
+        <v>0.0878667463580291</v>
       </c>
       <c r="W34">
-        <v>0.1334980729357239</v>
+        <v>0.1339011616346413</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.906125821817175</v>
+        <v>0.8786674635802909</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1626056019809427</v>
+        <v>0.1636156019809427</v>
       </c>
       <c r="C35">
-        <v>14.16125493394031</v>
+        <v>13.70775506120432</v>
       </c>
       <c r="D35">
-        <v>21.02015493394031</v>
+        <v>20.83995506120432</v>
       </c>
       <c r="E35">
-        <v>6.2889</v>
+        <v>6.562200000000001</v>
       </c>
       <c r="F35">
-        <v>9.0189</v>
+        <v>9.292200000000001</v>
       </c>
       <c r="G35">
         <v>2.16</v>
@@ -4282,37 +4282,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M35">
-        <v>1.32397452</v>
+        <v>1.36409496</v>
       </c>
       <c r="N35">
-        <v>-0.1606411866666668</v>
+        <v>-0.200761626666667</v>
       </c>
       <c r="O35">
-        <v>-0.01606411866666668</v>
+        <v>-0.0200761626666667</v>
       </c>
       <c r="P35">
-        <v>-0.1445770680000001</v>
+        <v>-0.1806854640000003</v>
       </c>
       <c r="Q35">
-        <v>-0.09057706800000009</v>
+        <v>-0.1266854640000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.176743609912703</v>
+        <v>0.1787276040022895</v>
       </c>
       <c r="T35">
-        <v>0.8008348177472954</v>
+        <v>0.8129686786222544</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.0878667463580291</v>
+        <v>0.0852824302886753</v>
       </c>
       <c r="W35">
-        <v>0.1339011616346413</v>
+        <v>0.1342805392336225</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8786674635802909</v>
+        <v>0.8528243028867529</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1636156019809427</v>
+        <v>0.1646256019809427</v>
       </c>
       <c r="C36">
-        <v>13.70775506120432</v>
+        <v>13.25731853287273</v>
       </c>
       <c r="D36">
-        <v>20.83995506120432</v>
+        <v>20.66281853287273</v>
       </c>
       <c r="E36">
-        <v>6.562200000000001</v>
+        <v>6.835500000000001</v>
       </c>
       <c r="F36">
-        <v>9.292200000000001</v>
+        <v>9.565500000000002</v>
       </c>
       <c r="G36">
         <v>2.16</v>
@@ -4364,37 +4364,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M36">
-        <v>1.36409496</v>
+        <v>1.4042154</v>
       </c>
       <c r="N36">
-        <v>-0.200761626666667</v>
+        <v>-0.2408820666666671</v>
       </c>
       <c r="O36">
-        <v>-0.0200761626666667</v>
+        <v>-0.02408820666666671</v>
       </c>
       <c r="P36">
-        <v>-0.1806854640000003</v>
+        <v>-0.2167938600000004</v>
       </c>
       <c r="Q36">
-        <v>-0.1266854640000002</v>
+        <v>-0.1627938600000003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1787276040022895</v>
+        <v>0.1807726440638631</v>
       </c>
       <c r="T36">
-        <v>0.8129686786222544</v>
+        <v>0.8254758890625967</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.0852824302886753</v>
+        <v>0.08284578942328456</v>
       </c>
       <c r="W36">
-        <v>0.1342805392336225</v>
+        <v>0.1346382381126618</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8528243028867529</v>
+        <v>0.8284578942328455</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1646256019809427</v>
+        <v>0.1656356019809427</v>
       </c>
       <c r="C37">
-        <v>13.25731853287273</v>
+        <v>12.80986789338647</v>
       </c>
       <c r="D37">
-        <v>20.66281853287273</v>
+        <v>20.48866789338647</v>
       </c>
       <c r="E37">
-        <v>6.835500000000001</v>
+        <v>7.108800000000002</v>
       </c>
       <c r="F37">
-        <v>9.565500000000002</v>
+        <v>9.838800000000003</v>
       </c>
       <c r="G37">
         <v>2.16</v>
@@ -4446,37 +4446,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M37">
-        <v>1.4042154</v>
+        <v>1.444335840000001</v>
       </c>
       <c r="N37">
-        <v>-0.2408820666666671</v>
+        <v>-0.2810025066666673</v>
       </c>
       <c r="O37">
-        <v>-0.02408820666666671</v>
+        <v>-0.02810025066666673</v>
       </c>
       <c r="P37">
-        <v>-0.2167938600000004</v>
+        <v>-0.2529022560000005</v>
       </c>
       <c r="Q37">
-        <v>-0.1627938600000003</v>
+        <v>-0.1989022560000005</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1807726440638631</v>
+        <v>0.182881591627361</v>
       </c>
       <c r="T37">
-        <v>0.8254758890625967</v>
+        <v>0.8383739498291999</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.08284578942328456</v>
+        <v>0.08054451749485998</v>
       </c>
       <c r="W37">
-        <v>0.1346382381126618</v>
+        <v>0.1349760648317546</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8284578942328455</v>
+        <v>0.8054451749485998</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1656356019809427</v>
+        <v>0.1873301435810436</v>
       </c>
       <c r="C38">
-        <v>12.80986789338648</v>
+        <v>9.395948893807793</v>
       </c>
       <c r="D38">
-        <v>20.48866789338648</v>
+        <v>17.34804889380779</v>
       </c>
       <c r="E38">
-        <v>7.1088</v>
+        <v>7.382099999999999</v>
       </c>
       <c r="F38">
-        <v>9.838800000000001</v>
+        <v>10.1121</v>
       </c>
       <c r="G38">
         <v>2.16</v>
@@ -4528,45 +4528,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M38">
-        <v>1.44433584</v>
+        <v>2.03050968</v>
       </c>
       <c r="N38">
-        <v>-0.281002506666667</v>
+        <v>-0.8671763466666669</v>
       </c>
       <c r="O38">
-        <v>-0.0281002506666667</v>
+        <v>-0.0867176346666667</v>
       </c>
       <c r="P38">
-        <v>-0.2529022560000003</v>
+        <v>-0.7804587120000002</v>
       </c>
       <c r="Q38">
-        <v>-0.1989022560000003</v>
+        <v>-0.7264587120000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.182881591627361</v>
+        <v>0.1861758099073205</v>
       </c>
       <c r="T38">
-        <v>0.8383739498291997</v>
+        <v>0.8585209787495872</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08054451749486</v>
+        <v>0.05729267606019654</v>
       </c>
       <c r="W38">
-        <v>0.1349760648317546</v>
+        <v>0.1892956306471126</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8054451749485999</v>
+        <v>0.5729267606019653</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1873301435810436</v>
+        <v>0.1888801435810435</v>
       </c>
       <c r="C39">
-        <v>9.395948893807793</v>
+        <v>8.934715927622506</v>
       </c>
       <c r="D39">
-        <v>17.34804889380779</v>
+        <v>17.16011592762251</v>
       </c>
       <c r="E39">
-        <v>7.382099999999999</v>
+        <v>7.6554</v>
       </c>
       <c r="F39">
-        <v>10.1121</v>
+        <v>10.3854</v>
       </c>
       <c r="G39">
         <v>2.16</v>
@@ -4610,37 +4610,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M39">
-        <v>2.03050968</v>
+        <v>2.08538832</v>
       </c>
       <c r="N39">
-        <v>-0.8671763466666669</v>
+        <v>-0.922054986666667</v>
       </c>
       <c r="O39">
-        <v>-0.0867176346666667</v>
+        <v>-0.0922054986666667</v>
       </c>
       <c r="P39">
-        <v>-0.7804587120000002</v>
+        <v>-0.8298494880000002</v>
       </c>
       <c r="Q39">
-        <v>-0.7264587120000001</v>
+        <v>-0.7758494880000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1861758099073205</v>
+        <v>0.1884399358735676</v>
       </c>
       <c r="T39">
-        <v>0.8585209787495872</v>
+        <v>0.8723680913100645</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.05729267606019654</v>
+        <v>0.05578497405861241</v>
       </c>
       <c r="W39">
-        <v>0.1892956306471126</v>
+        <v>0.1895983772090306</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5729267606019653</v>
+        <v>0.5578497405861241</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1888801435810435</v>
+        <v>0.1904301435810435</v>
       </c>
       <c r="C40">
-        <v>8.934715927622506</v>
+        <v>8.477511113389154</v>
       </c>
       <c r="D40">
-        <v>17.16011592762251</v>
+        <v>16.97621111338916</v>
       </c>
       <c r="E40">
-        <v>7.6554</v>
+        <v>7.928700000000001</v>
       </c>
       <c r="F40">
-        <v>10.3854</v>
+        <v>10.6587</v>
       </c>
       <c r="G40">
         <v>2.16</v>
@@ -4692,37 +4692,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M40">
-        <v>2.08538832</v>
+        <v>2.14026696</v>
       </c>
       <c r="N40">
-        <v>-0.922054986666667</v>
+        <v>-0.9769336266666671</v>
       </c>
       <c r="O40">
-        <v>-0.0922054986666667</v>
+        <v>-0.09769336266666671</v>
       </c>
       <c r="P40">
-        <v>-0.8298494880000002</v>
+        <v>-0.8792402640000003</v>
       </c>
       <c r="Q40">
-        <v>-0.7758494880000002</v>
+        <v>-0.8252402640000003</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1884399358735676</v>
+        <v>0.1907782954780523</v>
       </c>
       <c r="T40">
-        <v>0.8723680913100645</v>
+        <v>0.8866692075610492</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05578497405861241</v>
+        <v>0.05435459010839158</v>
       </c>
       <c r="W40">
-        <v>0.1895983772090306</v>
+        <v>0.189885598306235</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5578497405861241</v>
+        <v>0.5435459010839158</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1904301435810435</v>
+        <v>0.1919801435810435</v>
       </c>
       <c r="C41">
-        <v>8.477511113389154</v>
+        <v>8.024206315328705</v>
       </c>
       <c r="D41">
-        <v>16.97621111338916</v>
+        <v>16.79620631532871</v>
       </c>
       <c r="E41">
-        <v>7.928700000000001</v>
+        <v>8.202000000000002</v>
       </c>
       <c r="F41">
-        <v>10.6587</v>
+        <v>10.932</v>
       </c>
       <c r="G41">
         <v>2.16</v>
@@ -4774,37 +4774,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M41">
-        <v>2.14026696</v>
+        <v>2.1951456</v>
       </c>
       <c r="N41">
-        <v>-0.9769336266666671</v>
+        <v>-1.031812266666667</v>
       </c>
       <c r="O41">
-        <v>-0.09769336266666671</v>
+        <v>-0.1031812266666667</v>
       </c>
       <c r="P41">
-        <v>-0.8792402640000003</v>
+        <v>-0.9286310400000004</v>
       </c>
       <c r="Q41">
-        <v>-0.8252402640000003</v>
+        <v>-0.8746310400000004</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1907782954780523</v>
+        <v>0.1931946004026865</v>
       </c>
       <c r="T41">
-        <v>0.8866692075610492</v>
+        <v>0.9014470276870666</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05435459010839158</v>
+        <v>0.05299572535568179</v>
       </c>
       <c r="W41">
-        <v>0.189885598306235</v>
+        <v>0.1901584583485791</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5435459010839158</v>
+        <v>0.5299572535568179</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1919801435810435</v>
+        <v>0.1935301435810435</v>
       </c>
       <c r="C42">
-        <v>8.024206315328705</v>
+        <v>7.574678775317704</v>
       </c>
       <c r="D42">
-        <v>16.79620631532871</v>
+        <v>16.6199787753177</v>
       </c>
       <c r="E42">
-        <v>8.202000000000002</v>
+        <v>8.475300000000001</v>
       </c>
       <c r="F42">
-        <v>10.932</v>
+        <v>11.2053</v>
       </c>
       <c r="G42">
         <v>2.16</v>
@@ -4856,37 +4856,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M42">
-        <v>2.1951456</v>
+        <v>2.25002424</v>
       </c>
       <c r="N42">
-        <v>-1.031812266666667</v>
+        <v>-1.086690906666667</v>
       </c>
       <c r="O42">
-        <v>-0.1031812266666667</v>
+        <v>-0.1086690906666667</v>
       </c>
       <c r="P42">
-        <v>-0.9286310400000004</v>
+        <v>-0.978021816</v>
       </c>
       <c r="Q42">
-        <v>-0.8746310400000004</v>
+        <v>-0.924021816</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1931946004026865</v>
+        <v>0.1956928139688337</v>
       </c>
       <c r="T42">
-        <v>0.9014470276870666</v>
+        <v>0.9167257908682034</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05299572535568179</v>
+        <v>0.05170314668847005</v>
       </c>
       <c r="W42">
-        <v>0.1901584583485791</v>
+        <v>0.1904180081449552</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5299572535568179</v>
+        <v>0.5170314668847005</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1935301435810435</v>
+        <v>0.1950801435810435</v>
       </c>
       <c r="C43">
-        <v>7.574678775317704</v>
+        <v>7.128810833702905</v>
       </c>
       <c r="D43">
-        <v>16.6199787753177</v>
+        <v>16.44741083370291</v>
       </c>
       <c r="E43">
-        <v>8.475300000000001</v>
+        <v>8.748600000000001</v>
       </c>
       <c r="F43">
-        <v>11.2053</v>
+        <v>11.4786</v>
       </c>
       <c r="G43">
         <v>2.16</v>
@@ -4938,37 +4938,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M43">
-        <v>2.25002424</v>
+        <v>2.304902880000001</v>
       </c>
       <c r="N43">
-        <v>-1.086690906666667</v>
+        <v>-1.141569546666667</v>
       </c>
       <c r="O43">
-        <v>-0.1086690906666667</v>
+        <v>-0.1141569546666667</v>
       </c>
       <c r="P43">
-        <v>-0.978021816</v>
+        <v>-1.027412592000001</v>
       </c>
       <c r="Q43">
-        <v>-0.924021816</v>
+        <v>-0.9734125920000005</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1956928139688337</v>
+        <v>0.1982771728303653</v>
       </c>
       <c r="T43">
-        <v>0.9167257908682034</v>
+        <v>0.932531407952138</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.05170314668847005</v>
+        <v>0.0504721193863636</v>
       </c>
       <c r="W43">
-        <v>0.1904180081449552</v>
+        <v>0.1906651984272182</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5170314668847005</v>
+        <v>0.504721193863636</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1950801435810435</v>
+        <v>0.2119644346266031</v>
       </c>
       <c r="C44">
-        <v>7.128810833702907</v>
+        <v>5.184257462991118</v>
       </c>
       <c r="D44">
-        <v>16.44741083370291</v>
+        <v>14.77615746299112</v>
       </c>
       <c r="E44">
-        <v>8.7486</v>
+        <v>9.0219</v>
       </c>
       <c r="F44">
-        <v>11.4786</v>
+        <v>11.7519</v>
       </c>
       <c r="G44">
         <v>2.16</v>
@@ -5020,45 +5020,45 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M44">
-        <v>2.30490288</v>
+        <v>2.77109802</v>
       </c>
       <c r="N44">
-        <v>-1.141569546666667</v>
+        <v>-1.607764686666667</v>
       </c>
       <c r="O44">
-        <v>-0.1141569546666667</v>
+        <v>-0.1607764686666667</v>
       </c>
       <c r="P44">
-        <v>-1.027412592</v>
+        <v>-1.446988218</v>
       </c>
       <c r="Q44">
-        <v>-0.9734125920000001</v>
+        <v>-1.392988218</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1982771728303653</v>
+        <v>0.2014509671704761</v>
       </c>
       <c r="T44">
-        <v>0.932531407952138</v>
+        <v>0.9519419390473514</v>
       </c>
       <c r="U44">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05047211938636362</v>
+        <v>0.04198095213295029</v>
       </c>
       <c r="W44">
-        <v>0.1906651984272182</v>
+        <v>0.2259008914870503</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5047211938636361</v>
+        <v>0.4198095213295029</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2119644346266031</v>
+        <v>0.213864434626603</v>
       </c>
       <c r="C45">
-        <v>5.184257462991118</v>
+        <v>4.743910227553958</v>
       </c>
       <c r="D45">
-        <v>14.77615746299112</v>
+        <v>14.60911022755396</v>
       </c>
       <c r="E45">
-        <v>9.0219</v>
+        <v>9.295200000000001</v>
       </c>
       <c r="F45">
-        <v>11.7519</v>
+        <v>12.0252</v>
       </c>
       <c r="G45">
         <v>2.16</v>
@@ -5102,37 +5102,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M45">
-        <v>2.77109802</v>
+        <v>2.835542160000001</v>
       </c>
       <c r="N45">
-        <v>-1.607764686666667</v>
+        <v>-1.672208826666667</v>
       </c>
       <c r="O45">
-        <v>-0.1607764686666667</v>
+        <v>-0.1672208826666667</v>
       </c>
       <c r="P45">
-        <v>-1.446988218</v>
+        <v>-1.504987944</v>
       </c>
       <c r="Q45">
-        <v>-1.392988218</v>
+        <v>-1.450987944</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2014509671704761</v>
+        <v>0.2042304487270918</v>
       </c>
       <c r="T45">
-        <v>0.9519419390473514</v>
+        <v>0.9689409022446256</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04198095213295029</v>
+        <v>0.04102683958447415</v>
       </c>
       <c r="W45">
-        <v>0.2259008914870503</v>
+        <v>0.226125871225981</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4198095213295029</v>
+        <v>0.4102683958447414</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.213864434626603</v>
+        <v>0.2157644346266031</v>
       </c>
       <c r="C46">
-        <v>4.743910227553958</v>
+        <v>4.307297770490027</v>
       </c>
       <c r="D46">
-        <v>14.60911022755396</v>
+        <v>14.44579777049003</v>
       </c>
       <c r="E46">
-        <v>9.295200000000001</v>
+        <v>9.5685</v>
       </c>
       <c r="F46">
-        <v>12.0252</v>
+        <v>12.2985</v>
       </c>
       <c r="G46">
         <v>2.16</v>
@@ -5184,37 +5184,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M46">
-        <v>2.835542160000001</v>
+        <v>2.8999863</v>
       </c>
       <c r="N46">
-        <v>-1.672208826666667</v>
+        <v>-1.736652966666667</v>
       </c>
       <c r="O46">
-        <v>-0.1672208826666667</v>
+        <v>-0.1736652966666667</v>
       </c>
       <c r="P46">
-        <v>-1.504987944</v>
+        <v>-1.56298767</v>
       </c>
       <c r="Q46">
-        <v>-1.450987944</v>
+        <v>-1.50898767</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2042304487270918</v>
+        <v>0.2071110023403116</v>
       </c>
       <c r="T46">
-        <v>0.9689409022446256</v>
+        <v>0.9865580095581642</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04102683958447415</v>
+        <v>0.04011513203815251</v>
       </c>
       <c r="W46">
-        <v>0.226125871225981</v>
+        <v>0.2263408518654036</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4102683958447414</v>
+        <v>0.401151320381525</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2157644346266031</v>
+        <v>0.2176644346266031</v>
       </c>
       <c r="C47">
-        <v>4.307297770490027</v>
+        <v>3.874296225353225</v>
       </c>
       <c r="D47">
-        <v>14.44579777049003</v>
+        <v>14.28609622535323</v>
       </c>
       <c r="E47">
-        <v>9.5685</v>
+        <v>9.841800000000001</v>
       </c>
       <c r="F47">
-        <v>12.2985</v>
+        <v>12.5718</v>
       </c>
       <c r="G47">
         <v>2.16</v>
@@ -5266,37 +5266,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M47">
-        <v>2.8999863</v>
+        <v>2.964430440000001</v>
       </c>
       <c r="N47">
-        <v>-1.736652966666667</v>
+        <v>-1.801097106666667</v>
       </c>
       <c r="O47">
-        <v>-0.1736652966666667</v>
+        <v>-0.1801097106666667</v>
       </c>
       <c r="P47">
-        <v>-1.56298767</v>
+        <v>-1.620987396000001</v>
       </c>
       <c r="Q47">
-        <v>-1.50898767</v>
+        <v>-1.566987396</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2071110023403116</v>
+        <v>0.2100982431243915</v>
       </c>
       <c r="T47">
-        <v>0.9865580095581642</v>
+        <v>1.00482760232776</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04011513203815251</v>
+        <v>0.03924306395036657</v>
       </c>
       <c r="W47">
-        <v>0.2263408518654036</v>
+        <v>0.2265464855205036</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.401151320381525</v>
+        <v>0.3924306395036657</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2176644346266031</v>
+        <v>0.219564434626603</v>
       </c>
       <c r="C48">
-        <v>3.874296225353225</v>
+        <v>3.444787143290494</v>
       </c>
       <c r="D48">
-        <v>14.28609622535323</v>
+        <v>14.1298871432905</v>
       </c>
       <c r="E48">
-        <v>9.841800000000001</v>
+        <v>10.1151</v>
       </c>
       <c r="F48">
-        <v>12.5718</v>
+        <v>12.8451</v>
       </c>
       <c r="G48">
         <v>2.16</v>
@@ -5348,37 +5348,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M48">
-        <v>2.964430440000001</v>
+        <v>3.028874580000001</v>
       </c>
       <c r="N48">
-        <v>-1.801097106666667</v>
+        <v>-1.865541246666667</v>
       </c>
       <c r="O48">
-        <v>-0.1801097106666667</v>
+        <v>-0.1865541246666667</v>
       </c>
       <c r="P48">
-        <v>-1.620987396000001</v>
+        <v>-1.678987122000001</v>
       </c>
       <c r="Q48">
-        <v>-1.566987396</v>
+        <v>-1.624987122000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2100982431243915</v>
+        <v>0.2131982099757951</v>
       </c>
       <c r="T48">
-        <v>1.00482760232776</v>
+        <v>1.023786613692435</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03924306395036657</v>
+        <v>0.03840810514291196</v>
       </c>
       <c r="W48">
-        <v>0.2265464855205036</v>
+        <v>0.2267433688073014</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3924306395036657</v>
+        <v>0.3840810514291196</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.219564434626603</v>
+        <v>0.221464434626603</v>
       </c>
       <c r="C49">
-        <v>3.444787143290494</v>
+        <v>3.018657200056296</v>
       </c>
       <c r="D49">
-        <v>14.1298871432905</v>
+        <v>13.9770572000563</v>
       </c>
       <c r="E49">
-        <v>10.1151</v>
+        <v>10.3884</v>
       </c>
       <c r="F49">
-        <v>12.8451</v>
+        <v>13.1184</v>
       </c>
       <c r="G49">
         <v>2.16</v>
@@ -5430,37 +5430,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M49">
-        <v>3.028874580000001</v>
+        <v>3.093318720000001</v>
       </c>
       <c r="N49">
-        <v>-1.865541246666667</v>
+        <v>-1.929985386666667</v>
       </c>
       <c r="O49">
-        <v>-0.1865541246666667</v>
+        <v>-0.1929985386666667</v>
       </c>
       <c r="P49">
-        <v>-1.678987122000001</v>
+        <v>-1.736986848</v>
       </c>
       <c r="Q49">
-        <v>-1.624987122000001</v>
+        <v>-1.682986848</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2131982099757951</v>
+        <v>0.2164174063214835</v>
       </c>
       <c r="T49">
-        <v>1.023786613692435</v>
+        <v>1.043474817801904</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03840810514291196</v>
+        <v>0.03760793628576797</v>
       </c>
       <c r="W49">
-        <v>0.2267433688073014</v>
+        <v>0.2269320486238159</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3840810514291196</v>
+        <v>0.3760793628576796</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.221464434626603</v>
+        <v>0.223364434626603</v>
       </c>
       <c r="C50">
-        <v>3.018657200056296</v>
+        <v>2.595797921837368</v>
       </c>
       <c r="D50">
-        <v>13.9770572000563</v>
+        <v>13.82749792183737</v>
       </c>
       <c r="E50">
-        <v>10.3884</v>
+        <v>10.6617</v>
       </c>
       <c r="F50">
-        <v>13.1184</v>
+        <v>13.3917</v>
       </c>
       <c r="G50">
         <v>2.16</v>
@@ -5512,37 +5512,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M50">
-        <v>3.093318720000001</v>
+        <v>3.15776286</v>
       </c>
       <c r="N50">
-        <v>-1.929985386666667</v>
+        <v>-1.994429526666667</v>
       </c>
       <c r="O50">
-        <v>-0.1929985386666667</v>
+        <v>-0.1994429526666667</v>
       </c>
       <c r="P50">
-        <v>-1.736986848</v>
+        <v>-1.794986574</v>
       </c>
       <c r="Q50">
-        <v>-1.682986848</v>
+        <v>-1.740986574</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2164174063214835</v>
+        <v>0.2197628456611204</v>
       </c>
       <c r="T50">
-        <v>1.043474817801904</v>
+        <v>1.06393510834704</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03760793628576797</v>
+        <v>0.03684042738197679</v>
       </c>
       <c r="W50">
-        <v>0.2269320486238159</v>
+        <v>0.2271130272233299</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3760793628576796</v>
+        <v>0.3684042738197678</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.223364434626603</v>
+        <v>0.2252644346266031</v>
       </c>
       <c r="C51">
-        <v>2.595797921837368</v>
+        <v>2.176105428493745</v>
       </c>
       <c r="D51">
-        <v>13.82749792183737</v>
+        <v>13.68110542849375</v>
       </c>
       <c r="E51">
-        <v>10.6617</v>
+        <v>10.935</v>
       </c>
       <c r="F51">
-        <v>13.3917</v>
+        <v>13.665</v>
       </c>
       <c r="G51">
         <v>2.16</v>
@@ -5594,37 +5594,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M51">
-        <v>3.15776286</v>
+        <v>3.222207</v>
       </c>
       <c r="N51">
-        <v>-1.994429526666667</v>
+        <v>-2.058873666666667</v>
       </c>
       <c r="O51">
-        <v>-0.1994429526666667</v>
+        <v>-0.2058873666666667</v>
       </c>
       <c r="P51">
-        <v>-1.794986574</v>
+        <v>-1.8529863</v>
       </c>
       <c r="Q51">
-        <v>-1.740986574</v>
+        <v>-1.7989863</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2197628456611204</v>
+        <v>0.2232421025743428</v>
       </c>
       <c r="T51">
-        <v>1.06393510834704</v>
+        <v>1.085213810513981</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03684042738197679</v>
+        <v>0.03610361883433725</v>
       </c>
       <c r="W51">
-        <v>0.2271130272233299</v>
+        <v>0.2272867666788633</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3684042738197678</v>
+        <v>0.3610361883433725</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2252644346266031</v>
+        <v>0.227164434626603</v>
       </c>
       <c r="C52">
-        <v>2.176105428493745</v>
+        <v>1.759480192938854</v>
       </c>
       <c r="D52">
-        <v>13.68110542849375</v>
+        <v>13.53778019293886</v>
       </c>
       <c r="E52">
-        <v>10.935</v>
+        <v>11.2083</v>
       </c>
       <c r="F52">
-        <v>13.665</v>
+        <v>13.9383</v>
       </c>
       <c r="G52">
         <v>2.16</v>
@@ -5676,37 +5676,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M52">
-        <v>3.222207</v>
+        <v>3.28665114</v>
       </c>
       <c r="N52">
-        <v>-2.058873666666667</v>
+        <v>-2.123317806666667</v>
       </c>
       <c r="O52">
-        <v>-0.2058873666666667</v>
+        <v>-0.2123317806666667</v>
       </c>
       <c r="P52">
-        <v>-1.8529863</v>
+        <v>-1.910986026</v>
       </c>
       <c r="Q52">
-        <v>-1.7989863</v>
+        <v>-1.856986026</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2232421025743428</v>
+        <v>0.2268633699738192</v>
       </c>
       <c r="T52">
-        <v>1.085213810513981</v>
+        <v>1.107361031136715</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03610361883433725</v>
+        <v>0.03539570473954632</v>
       </c>
       <c r="W52">
-        <v>0.2272867666788633</v>
+        <v>0.227453692822415</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3610361883433725</v>
+        <v>0.3539570473954633</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.227164434626603</v>
+        <v>0.2290644346266031</v>
       </c>
       <c r="C53">
-        <v>1.759480192938854</v>
+        <v>1.345826815487351</v>
       </c>
       <c r="D53">
-        <v>13.53778019293886</v>
+        <v>13.39742681548735</v>
       </c>
       <c r="E53">
-        <v>11.2083</v>
+        <v>11.4816</v>
       </c>
       <c r="F53">
-        <v>13.9383</v>
+        <v>14.2116</v>
       </c>
       <c r="G53">
         <v>2.16</v>
@@ -5758,37 +5758,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M53">
-        <v>3.28665114</v>
+        <v>3.35109528</v>
       </c>
       <c r="N53">
-        <v>-2.123317806666667</v>
+        <v>-2.187761946666667</v>
       </c>
       <c r="O53">
-        <v>-0.2123317806666667</v>
+        <v>-0.2187761946666667</v>
       </c>
       <c r="P53">
-        <v>-1.910986026</v>
+        <v>-1.968985752</v>
       </c>
       <c r="Q53">
-        <v>-1.856986026</v>
+        <v>-1.914985752</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2268633699738192</v>
+        <v>0.2306355235149404</v>
       </c>
       <c r="T53">
-        <v>1.107361031136715</v>
+        <v>1.13043105261873</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03539570473954632</v>
+        <v>0.03471501810993966</v>
       </c>
       <c r="W53">
-        <v>0.227453692822415</v>
+        <v>0.2276141987296762</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3539570473954633</v>
+        <v>0.3471501810993967</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2290644346266031</v>
+        <v>0.230964434626603</v>
       </c>
       <c r="C54">
-        <v>1.345826815487351</v>
+        <v>0.9350538120957541</v>
       </c>
       <c r="D54">
-        <v>13.39742681548735</v>
+        <v>13.25995381209576</v>
       </c>
       <c r="E54">
-        <v>11.4816</v>
+        <v>11.7549</v>
       </c>
       <c r="F54">
-        <v>14.2116</v>
+        <v>14.4849</v>
       </c>
       <c r="G54">
         <v>2.16</v>
@@ -5840,37 +5840,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M54">
-        <v>3.35109528</v>
+        <v>3.41553942</v>
       </c>
       <c r="N54">
-        <v>-2.187761946666667</v>
+        <v>-2.252206086666667</v>
       </c>
       <c r="O54">
-        <v>-0.2187761946666667</v>
+        <v>-0.2252206086666667</v>
       </c>
       <c r="P54">
-        <v>-1.968985752</v>
+        <v>-2.026985478</v>
       </c>
       <c r="Q54">
-        <v>-1.914985752</v>
+        <v>-1.972985478</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2306355235149404</v>
+        <v>0.2345681942280243</v>
       </c>
       <c r="T54">
-        <v>1.13043105261873</v>
+        <v>1.154482777142533</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03471501810993966</v>
+        <v>0.03406001776824268</v>
       </c>
       <c r="W54">
-        <v>0.2276141987296762</v>
+        <v>0.2277686478102484</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3471501810993967</v>
+        <v>0.3406001776824269</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.230964434626603</v>
+        <v>0.2328644346266031</v>
       </c>
       <c r="C55">
-        <v>0.9350538120957541</v>
+        <v>0.5270734155079637</v>
       </c>
       <c r="D55">
-        <v>13.25995381209576</v>
+        <v>13.12527341550797</v>
       </c>
       <c r="E55">
-        <v>11.7549</v>
+        <v>12.0282</v>
       </c>
       <c r="F55">
-        <v>14.4849</v>
+        <v>14.7582</v>
       </c>
       <c r="G55">
         <v>2.16</v>
@@ -5922,37 +5922,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M55">
-        <v>3.41553942</v>
+        <v>3.479983560000001</v>
       </c>
       <c r="N55">
-        <v>-2.252206086666667</v>
+        <v>-2.316650226666668</v>
       </c>
       <c r="O55">
-        <v>-0.2252206086666667</v>
+        <v>-0.2316650226666668</v>
       </c>
       <c r="P55">
-        <v>-2.026985478</v>
+        <v>-2.084985204000001</v>
       </c>
       <c r="Q55">
-        <v>-1.972985478</v>
+        <v>-2.030985204000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2345681942280243</v>
+        <v>0.2386718506242857</v>
       </c>
       <c r="T55">
-        <v>1.154482777142533</v>
+        <v>1.179580228819544</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03406001776824268</v>
+        <v>0.03342927669846041</v>
       </c>
       <c r="W55">
-        <v>0.2277686478102484</v>
+        <v>0.227917376554503</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3406001776824269</v>
+        <v>0.3342927669846041</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2328644346266031</v>
+        <v>0.2347644346266031</v>
       </c>
       <c r="C56">
-        <v>0.5270734155079637</v>
+        <v>0.1218013883974454</v>
       </c>
       <c r="D56">
-        <v>13.12527341550797</v>
+        <v>12.99330138839745</v>
       </c>
       <c r="E56">
-        <v>12.0282</v>
+        <v>12.3015</v>
       </c>
       <c r="F56">
-        <v>14.7582</v>
+        <v>15.0315</v>
       </c>
       <c r="G56">
         <v>2.16</v>
@@ -6004,37 +6004,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M56">
-        <v>3.479983560000001</v>
+        <v>3.544427700000001</v>
       </c>
       <c r="N56">
-        <v>-2.316650226666668</v>
+        <v>-2.381094366666668</v>
       </c>
       <c r="O56">
-        <v>-0.2316650226666668</v>
+        <v>-0.2381094366666668</v>
       </c>
       <c r="P56">
-        <v>-2.084985204000001</v>
+        <v>-2.142984930000001</v>
       </c>
       <c r="Q56">
-        <v>-2.030985204000001</v>
+        <v>-2.088984930000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2386718506242857</v>
+        <v>0.2429578917492698</v>
       </c>
       <c r="T56">
-        <v>1.179580228819544</v>
+        <v>1.205793122793312</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03342927669846041</v>
+        <v>0.03282147166757931</v>
       </c>
       <c r="W56">
-        <v>0.227917376554503</v>
+        <v>0.2280606969807848</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3342927669846041</v>
+        <v>0.3282147166757931</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2347644346266031</v>
+        <v>0.2366644346266031</v>
       </c>
       <c r="C57">
-        <v>0.1218013883974454</v>
+        <v>-0.2808431523298598</v>
       </c>
       <c r="D57">
-        <v>12.99330138839745</v>
+        <v>12.86395684767014</v>
       </c>
       <c r="E57">
-        <v>12.3015</v>
+        <v>12.5748</v>
       </c>
       <c r="F57">
-        <v>15.0315</v>
+        <v>15.3048</v>
       </c>
       <c r="G57">
         <v>2.16</v>
@@ -6086,37 +6086,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M57">
-        <v>3.544427700000001</v>
+        <v>3.608871840000001</v>
       </c>
       <c r="N57">
-        <v>-2.381094366666668</v>
+        <v>-2.445538506666668</v>
       </c>
       <c r="O57">
-        <v>-0.2381094366666668</v>
+        <v>-0.2445538506666668</v>
       </c>
       <c r="P57">
-        <v>-2.142984930000001</v>
+        <v>-2.200984656000001</v>
       </c>
       <c r="Q57">
-        <v>-2.088984930000001</v>
+        <v>-2.146984656000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2429578917492698</v>
+        <v>0.2474387529253896</v>
       </c>
       <c r="T57">
-        <v>1.205793122793312</v>
+        <v>1.233197511947705</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03282147166757931</v>
+        <v>0.03223537395922968</v>
       </c>
       <c r="W57">
-        <v>0.2280606969807848</v>
+        <v>0.2281988988204136</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3282147166757931</v>
+        <v>0.3223537395922967</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2366644346266031</v>
+        <v>0.2385644346266031</v>
       </c>
       <c r="C58">
-        <v>-0.2808431523298598</v>
+        <v>-0.6809379008420446</v>
       </c>
       <c r="D58">
-        <v>12.86395684767014</v>
+        <v>12.73716209915796</v>
       </c>
       <c r="E58">
-        <v>12.5748</v>
+        <v>12.8481</v>
       </c>
       <c r="F58">
-        <v>15.3048</v>
+        <v>15.5781</v>
       </c>
       <c r="G58">
         <v>2.16</v>
@@ -6168,37 +6168,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M58">
-        <v>3.608871840000001</v>
+        <v>3.673315980000001</v>
       </c>
       <c r="N58">
-        <v>-2.445538506666668</v>
+        <v>-2.509982646666668</v>
       </c>
       <c r="O58">
-        <v>-0.2445538506666668</v>
+        <v>-0.2509982646666668</v>
       </c>
       <c r="P58">
-        <v>-2.200984656000001</v>
+        <v>-2.258984382000001</v>
       </c>
       <c r="Q58">
-        <v>-2.146984656000001</v>
+        <v>-2.204984382000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2474387529253896</v>
+        <v>0.2521280262492359</v>
       </c>
       <c r="T58">
-        <v>1.233197511947705</v>
+        <v>1.261876523853466</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03223537395922968</v>
+        <v>0.03166984108275197</v>
       </c>
       <c r="W58">
-        <v>0.2281988988204136</v>
+        <v>0.2283322514726871</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3223537395922967</v>
+        <v>0.3166984108275196</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2385644346266031</v>
+        <v>0.2404644346266031</v>
       </c>
       <c r="C59">
-        <v>-0.6809379008420446</v>
+        <v>-1.07855751800694</v>
       </c>
       <c r="D59">
-        <v>12.73716209915796</v>
+        <v>12.61284248199306</v>
       </c>
       <c r="E59">
-        <v>12.8481</v>
+        <v>13.1214</v>
       </c>
       <c r="F59">
-        <v>15.5781</v>
+        <v>15.8514</v>
       </c>
       <c r="G59">
         <v>2.16</v>
@@ -6250,37 +6250,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M59">
-        <v>3.673315980000001</v>
+        <v>3.737760120000001</v>
       </c>
       <c r="N59">
-        <v>-2.509982646666668</v>
+        <v>-2.574426786666668</v>
       </c>
       <c r="O59">
-        <v>-0.2509982646666668</v>
+        <v>-0.2574426786666668</v>
       </c>
       <c r="P59">
-        <v>-2.258984382000001</v>
+        <v>-2.316984108000001</v>
       </c>
       <c r="Q59">
-        <v>-2.204984382000001</v>
+        <v>-2.262984108000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2521280262492359</v>
+        <v>0.2570405983027891</v>
       </c>
       <c r="T59">
-        <v>1.261876523853466</v>
+        <v>1.291921202992834</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03166984108275197</v>
+        <v>0.0311238093399459</v>
       </c>
       <c r="W59">
-        <v>0.2283322514726871</v>
+        <v>0.2284610057576408</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3166984108275196</v>
+        <v>0.311238093399459</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2404644346266031</v>
+        <v>0.2423644346266031</v>
       </c>
       <c r="C60">
-        <v>-1.078557518006937</v>
+        <v>-1.473773777992168</v>
       </c>
       <c r="D60">
-        <v>12.61284248199306</v>
+        <v>12.49092622200783</v>
       </c>
       <c r="E60">
-        <v>13.1214</v>
+        <v>13.3947</v>
       </c>
       <c r="F60">
-        <v>15.8514</v>
+        <v>16.1247</v>
       </c>
       <c r="G60">
         <v>2.16</v>
@@ -6332,37 +6332,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M60">
-        <v>3.73776012</v>
+        <v>3.80220426</v>
       </c>
       <c r="N60">
-        <v>-2.574426786666667</v>
+        <v>-2.638870926666667</v>
       </c>
       <c r="O60">
-        <v>-0.2574426786666667</v>
+        <v>-0.2638870926666667</v>
       </c>
       <c r="P60">
-        <v>-2.316984108</v>
+        <v>-2.374983834</v>
       </c>
       <c r="Q60">
-        <v>-2.262984108</v>
+        <v>-2.320983834</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.257040598302789</v>
+        <v>0.2621928080174912</v>
       </c>
       <c r="T60">
-        <v>1.291921202992834</v>
+        <v>1.323431476236562</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0311238093399459</v>
+        <v>0.03059628714774343</v>
       </c>
       <c r="W60">
-        <v>0.2284610057576408</v>
+        <v>0.2285853954905621</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3112380933994591</v>
+        <v>0.3059628714774344</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2423644346266031</v>
+        <v>0.244264434626603</v>
       </c>
       <c r="C61">
-        <v>-1.473773777992168</v>
+        <v>-1.866655706444314</v>
       </c>
       <c r="D61">
-        <v>12.49092622200783</v>
+        <v>12.37134429355569</v>
       </c>
       <c r="E61">
-        <v>13.3947</v>
+        <v>13.668</v>
       </c>
       <c r="F61">
-        <v>16.1247</v>
+        <v>16.398</v>
       </c>
       <c r="G61">
         <v>2.16</v>
@@ -6414,37 +6414,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M61">
-        <v>3.80220426</v>
+        <v>3.8666484</v>
       </c>
       <c r="N61">
-        <v>-2.638870926666667</v>
+        <v>-2.703315066666667</v>
       </c>
       <c r="O61">
-        <v>-0.2638870926666667</v>
+        <v>-0.2703315066666667</v>
       </c>
       <c r="P61">
-        <v>-2.374983834</v>
+        <v>-2.43298356</v>
       </c>
       <c r="Q61">
-        <v>-2.320983834</v>
+        <v>-2.37898356</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2621928080174912</v>
+        <v>0.2676026282179285</v>
       </c>
       <c r="T61">
-        <v>1.323431476236562</v>
+        <v>1.356517263142476</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03059628714774343</v>
+        <v>0.03008634902861438</v>
       </c>
       <c r="W61">
-        <v>0.2285853954905621</v>
+        <v>0.2287056388990527</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3059628714774344</v>
+        <v>0.3008634902861437</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.244264434626603</v>
+        <v>0.246164434626603</v>
       </c>
       <c r="C62">
-        <v>-1.866655706444314</v>
+        <v>-2.257269710806222</v>
       </c>
       <c r="D62">
-        <v>12.37134429355569</v>
+        <v>12.25403028919378</v>
       </c>
       <c r="E62">
-        <v>13.668</v>
+        <v>13.9413</v>
       </c>
       <c r="F62">
-        <v>16.398</v>
+        <v>16.6713</v>
       </c>
       <c r="G62">
         <v>2.16</v>
@@ -6496,37 +6496,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M62">
-        <v>3.8666484</v>
+        <v>3.931092540000001</v>
       </c>
       <c r="N62">
-        <v>-2.703315066666667</v>
+        <v>-2.767759206666668</v>
       </c>
       <c r="O62">
-        <v>-0.2703315066666667</v>
+        <v>-0.2767759206666668</v>
       </c>
       <c r="P62">
-        <v>-2.43298356</v>
+        <v>-2.490983286000001</v>
       </c>
       <c r="Q62">
-        <v>-2.37898356</v>
+        <v>-2.436983286000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2676026282179285</v>
+        <v>0.2732898750953113</v>
       </c>
       <c r="T62">
-        <v>1.356517263142476</v>
+        <v>1.391299757069206</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03008634902861438</v>
+        <v>0.02959313019207971</v>
       </c>
       <c r="W62">
-        <v>0.2287056388990527</v>
+        <v>0.2288219399007076</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3008634902861437</v>
+        <v>0.2959313019207971</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.246164434626603</v>
+        <v>0.248064434626603</v>
       </c>
       <c r="C63">
-        <v>-2.257269710806222</v>
+        <v>-2.645679703289328</v>
       </c>
       <c r="D63">
-        <v>12.25403028919378</v>
+        <v>12.13892029671067</v>
       </c>
       <c r="E63">
-        <v>13.9413</v>
+        <v>14.2146</v>
       </c>
       <c r="F63">
-        <v>16.6713</v>
+        <v>16.9446</v>
       </c>
       <c r="G63">
         <v>2.16</v>
@@ -6578,37 +6578,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M63">
-        <v>3.931092540000001</v>
+        <v>3.99553668</v>
       </c>
       <c r="N63">
-        <v>-2.767759206666668</v>
+        <v>-2.832203346666667</v>
       </c>
       <c r="O63">
-        <v>-0.2767759206666668</v>
+        <v>-0.2832203346666667</v>
       </c>
       <c r="P63">
-        <v>-2.490983286000001</v>
+        <v>-2.548983012</v>
       </c>
       <c r="Q63">
-        <v>-2.436983286000001</v>
+        <v>-2.494983012</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2732898750953113</v>
+        <v>0.2792764507557142</v>
       </c>
       <c r="T63">
-        <v>1.391299757069206</v>
+        <v>1.427912908571027</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02959313019207971</v>
+        <v>0.02911582164059456</v>
       </c>
       <c r="W63">
-        <v>0.2288219399007076</v>
+        <v>0.2289344892571478</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2959313019207971</v>
+        <v>0.2911582164059456</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.248064434626603</v>
+        <v>0.2499644346266031</v>
       </c>
       <c r="C64">
-        <v>-2.645679703289328</v>
+        <v>-3.031947216979615</v>
       </c>
       <c r="D64">
-        <v>12.13892029671067</v>
+        <v>12.02595278302038</v>
       </c>
       <c r="E64">
-        <v>14.2146</v>
+        <v>14.4879</v>
       </c>
       <c r="F64">
-        <v>16.9446</v>
+        <v>17.2179</v>
       </c>
       <c r="G64">
         <v>2.16</v>
@@ -6660,37 +6660,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M64">
-        <v>3.99553668</v>
+        <v>4.05998082</v>
       </c>
       <c r="N64">
-        <v>-2.832203346666667</v>
+        <v>-2.896647486666667</v>
       </c>
       <c r="O64">
-        <v>-0.2832203346666667</v>
+        <v>-0.2896647486666667</v>
       </c>
       <c r="P64">
-        <v>-2.548983012</v>
+        <v>-2.606982738</v>
       </c>
       <c r="Q64">
-        <v>-2.494983012</v>
+        <v>-2.552982738</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2792764507557142</v>
+        <v>0.2855866251004632</v>
       </c>
       <c r="T64">
-        <v>1.427912908571027</v>
+        <v>1.466505149343217</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02911582164059456</v>
+        <v>0.02865366574153751</v>
       </c>
       <c r="W64">
-        <v>0.2289344892571478</v>
+        <v>0.2290434656181455</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2911582164059456</v>
+        <v>0.2865366574153749</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2499644346266031</v>
+        <v>0.2518644346266031</v>
       </c>
       <c r="C65">
-        <v>-3.031947216979615</v>
+        <v>-3.416131515520231</v>
       </c>
       <c r="D65">
-        <v>12.02595278302038</v>
+        <v>11.91506848447977</v>
       </c>
       <c r="E65">
-        <v>14.4879</v>
+        <v>14.7612</v>
       </c>
       <c r="F65">
-        <v>17.2179</v>
+        <v>17.4912</v>
       </c>
       <c r="G65">
         <v>2.16</v>
@@ -6742,37 +6742,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M65">
-        <v>4.05998082</v>
+        <v>4.124424960000001</v>
       </c>
       <c r="N65">
-        <v>-2.896647486666667</v>
+        <v>-2.961091626666668</v>
       </c>
       <c r="O65">
-        <v>-0.2896647486666667</v>
+        <v>-0.2961091626666668</v>
       </c>
       <c r="P65">
-        <v>-2.606982738</v>
+        <v>-2.664982464000001</v>
       </c>
       <c r="Q65">
-        <v>-2.552982738</v>
+        <v>-2.610982464000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2855866251004632</v>
+        <v>0.2922473646865872</v>
       </c>
       <c r="T65">
-        <v>1.466505149343217</v>
+        <v>1.50724140349164</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02865366574153751</v>
+        <v>0.02820595221432598</v>
       </c>
       <c r="W65">
-        <v>0.2290434656181455</v>
+        <v>0.2291490364678619</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2865366574153749</v>
+        <v>0.2820595221432597</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2518644346266031</v>
+        <v>0.253764434626603</v>
       </c>
       <c r="C66">
-        <v>-3.416131515520231</v>
+        <v>-3.798289696781648</v>
       </c>
       <c r="D66">
-        <v>11.91506848447977</v>
+        <v>11.80621030321835</v>
       </c>
       <c r="E66">
-        <v>14.7612</v>
+        <v>15.0345</v>
       </c>
       <c r="F66">
-        <v>17.4912</v>
+        <v>17.7645</v>
       </c>
       <c r="G66">
         <v>2.16</v>
@@ -6824,37 +6824,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M66">
-        <v>4.124424960000001</v>
+        <v>4.188869100000001</v>
       </c>
       <c r="N66">
-        <v>-2.961091626666668</v>
+        <v>-3.025535766666668</v>
       </c>
       <c r="O66">
-        <v>-0.2961091626666668</v>
+        <v>-0.3025535766666668</v>
       </c>
       <c r="P66">
-        <v>-2.664982464000001</v>
+        <v>-2.722982190000001</v>
       </c>
       <c r="Q66">
-        <v>-2.610982464000001</v>
+        <v>-2.66898219</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2922473646865872</v>
+        <v>0.2992887179633469</v>
       </c>
       <c r="T66">
-        <v>1.50724140349164</v>
+        <v>1.550305443591401</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02820595221432598</v>
+        <v>0.02777201448795173</v>
       </c>
       <c r="W66">
-        <v>0.2291490364678619</v>
+        <v>0.229251358983741</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2820595221432597</v>
+        <v>0.2777201448795172</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.253764434626603</v>
+        <v>0.255664434626603</v>
       </c>
       <c r="C67">
-        <v>-3.798289696781648</v>
+        <v>-4.17847679090041</v>
       </c>
       <c r="D67">
-        <v>11.80621030321835</v>
+        <v>11.69932320909959</v>
       </c>
       <c r="E67">
-        <v>15.0345</v>
+        <v>15.3078</v>
       </c>
       <c r="F67">
-        <v>17.7645</v>
+        <v>18.0378</v>
       </c>
       <c r="G67">
         <v>2.16</v>
@@ -6906,37 +6906,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M67">
-        <v>4.188869100000001</v>
+        <v>4.253313240000001</v>
       </c>
       <c r="N67">
-        <v>-3.025535766666668</v>
+        <v>-3.089979906666668</v>
       </c>
       <c r="O67">
-        <v>-0.3025535766666668</v>
+        <v>-0.3089979906666668</v>
       </c>
       <c r="P67">
-        <v>-2.722982190000001</v>
+        <v>-2.780981916000001</v>
       </c>
       <c r="Q67">
-        <v>-2.66898219</v>
+        <v>-2.726981916000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2992887179633469</v>
+        <v>0.3067442684916806</v>
       </c>
       <c r="T67">
-        <v>1.550305443591401</v>
+        <v>1.59590266252056</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02777201448795173</v>
+        <v>0.02735122638964943</v>
       </c>
       <c r="W67">
-        <v>0.229251358983741</v>
+        <v>0.2293505808173207</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2777201448795172</v>
+        <v>0.2735122638964942</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.255664434626603</v>
+        <v>0.2575644346266031</v>
       </c>
       <c r="C68">
-        <v>-4.17847679090041</v>
+        <v>-4.556745853040072</v>
       </c>
       <c r="D68">
-        <v>11.69932320909959</v>
+        <v>11.59435414695993</v>
       </c>
       <c r="E68">
-        <v>15.3078</v>
+        <v>15.5811</v>
       </c>
       <c r="F68">
-        <v>18.0378</v>
+        <v>18.3111</v>
       </c>
       <c r="G68">
         <v>2.16</v>
@@ -6988,37 +6988,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M68">
-        <v>4.253313240000001</v>
+        <v>4.317757380000001</v>
       </c>
       <c r="N68">
-        <v>-3.089979906666668</v>
+        <v>-3.154424046666668</v>
       </c>
       <c r="O68">
-        <v>-0.3089979906666668</v>
+        <v>-0.3154424046666668</v>
       </c>
       <c r="P68">
-        <v>-2.780981916000001</v>
+        <v>-2.838981642000001</v>
       </c>
       <c r="Q68">
-        <v>-2.726981916000001</v>
+        <v>-2.784981642000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3067442684916806</v>
+        <v>0.3146516705671861</v>
       </c>
       <c r="T68">
-        <v>1.59590266252056</v>
+        <v>1.644263349263607</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02735122638964943</v>
+        <v>0.02694299913010242</v>
       </c>
       <c r="W68">
-        <v>0.2293505808173207</v>
+        <v>0.2294468408051218</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2735122638964942</v>
+        <v>0.2694299913010242</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2575644346266031</v>
+        <v>0.2594644346266031</v>
       </c>
       <c r="C69">
-        <v>-4.556745853040072</v>
+        <v>-4.933148051202913</v>
       </c>
       <c r="D69">
-        <v>11.59435414695993</v>
+        <v>11.49125194879709</v>
       </c>
       <c r="E69">
-        <v>15.5811</v>
+        <v>15.8544</v>
       </c>
       <c r="F69">
-        <v>18.3111</v>
+        <v>18.5844</v>
       </c>
       <c r="G69">
         <v>2.16</v>
@@ -7070,37 +7070,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M69">
-        <v>4.317757380000001</v>
+        <v>4.382201520000001</v>
       </c>
       <c r="N69">
-        <v>-3.154424046666668</v>
+        <v>-3.218868186666668</v>
       </c>
       <c r="O69">
-        <v>-0.3154424046666668</v>
+        <v>-0.3218868186666668</v>
       </c>
       <c r="P69">
-        <v>-2.838981642000001</v>
+        <v>-2.896981368000001</v>
       </c>
       <c r="Q69">
-        <v>-2.784981642000001</v>
+        <v>-2.842981368</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3146516705671861</v>
+        <v>0.3230532852724107</v>
       </c>
       <c r="T69">
-        <v>1.644263349263607</v>
+        <v>1.695646578928095</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02694299913010242</v>
+        <v>0.02654677855465974</v>
       </c>
       <c r="W69">
-        <v>0.2294468408051218</v>
+        <v>0.2295402696168113</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2694299913010242</v>
+        <v>0.2654677855465973</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2594644346266031</v>
+        <v>0.2613644346266031</v>
       </c>
       <c r="C70">
-        <v>-4.933148051202913</v>
+        <v>-5.307732749397834</v>
       </c>
       <c r="D70">
-        <v>11.49125194879709</v>
+        <v>11.38996725060217</v>
       </c>
       <c r="E70">
-        <v>15.8544</v>
+        <v>16.1277</v>
       </c>
       <c r="F70">
-        <v>18.5844</v>
+        <v>18.8577</v>
       </c>
       <c r="G70">
         <v>2.16</v>
@@ -7152,37 +7152,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M70">
-        <v>4.382201520000001</v>
+        <v>4.446645660000001</v>
       </c>
       <c r="N70">
-        <v>-3.218868186666668</v>
+        <v>-3.283312326666668</v>
       </c>
       <c r="O70">
-        <v>-0.3218868186666668</v>
+        <v>-0.3283312326666668</v>
       </c>
       <c r="P70">
-        <v>-2.896981368000001</v>
+        <v>-2.954981094000001</v>
       </c>
       <c r="Q70">
-        <v>-2.842981368</v>
+        <v>-2.900981094</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3230532852724107</v>
+        <v>0.3319969396360369</v>
       </c>
       <c r="T70">
-        <v>1.695646578928095</v>
+        <v>1.750344855667711</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02654677855465974</v>
+        <v>0.02616204263357771</v>
       </c>
       <c r="W70">
-        <v>0.2295402696168113</v>
+        <v>0.2296309903470024</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2654677855465973</v>
+        <v>0.2616204263357771</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2613644346266031</v>
+        <v>0.263264434626603</v>
       </c>
       <c r="C71">
-        <v>-5.307732749397834</v>
+        <v>-5.680547586448331</v>
       </c>
       <c r="D71">
-        <v>11.38996725060217</v>
+        <v>11.29045241355167</v>
       </c>
       <c r="E71">
-        <v>16.1277</v>
+        <v>16.401</v>
       </c>
       <c r="F71">
-        <v>18.8577</v>
+        <v>19.131</v>
       </c>
       <c r="G71">
         <v>2.16</v>
@@ -7234,37 +7234,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M71">
-        <v>4.446645660000001</v>
+        <v>4.511089800000001</v>
       </c>
       <c r="N71">
-        <v>-3.283312326666668</v>
+        <v>-3.347756466666668</v>
       </c>
       <c r="O71">
-        <v>-0.3283312326666668</v>
+        <v>-0.3347756466666669</v>
       </c>
       <c r="P71">
-        <v>-2.954981094000001</v>
+        <v>-3.012980820000001</v>
       </c>
       <c r="Q71">
-        <v>-2.900981094</v>
+        <v>-2.958980820000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3319969396360369</v>
+        <v>0.3415368376239047</v>
       </c>
       <c r="T71">
-        <v>1.750344855667711</v>
+        <v>1.808689684189968</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02616204263357771</v>
+        <v>0.02578829916738375</v>
       </c>
       <c r="W71">
-        <v>0.2296309903470024</v>
+        <v>0.2297191190563309</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2616204263357771</v>
+        <v>0.2578829916738373</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.263264434626603</v>
+        <v>0.2651644346266031</v>
       </c>
       <c r="C72">
-        <v>-5.680547586448331</v>
+        <v>-6.05163855070497</v>
       </c>
       <c r="D72">
-        <v>11.29045241355167</v>
+        <v>11.19266144929503</v>
       </c>
       <c r="E72">
-        <v>16.401</v>
+        <v>16.6743</v>
       </c>
       <c r="F72">
-        <v>19.131</v>
+        <v>19.4043</v>
       </c>
       <c r="G72">
         <v>2.16</v>
@@ -7316,37 +7316,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M72">
-        <v>4.511089800000001</v>
+        <v>4.575533940000001</v>
       </c>
       <c r="N72">
-        <v>-3.347756466666668</v>
+        <v>-3.412200606666667</v>
       </c>
       <c r="O72">
-        <v>-0.3347756466666669</v>
+        <v>-0.3412200606666668</v>
       </c>
       <c r="P72">
-        <v>-3.012980820000001</v>
+        <v>-3.070980546000001</v>
       </c>
       <c r="Q72">
-        <v>-2.958980820000002</v>
+        <v>-3.016980546000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3415368376239047</v>
+        <v>0.3517346596109359</v>
       </c>
       <c r="T72">
-        <v>1.808689684189968</v>
+        <v>1.871058293989622</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02578829916738375</v>
+        <v>0.02542508368615299</v>
       </c>
       <c r="W72">
-        <v>0.2297191190563309</v>
+        <v>0.2298047652668051</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2578829916738373</v>
+        <v>0.2542508368615298</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2651644346266031</v>
+        <v>0.2670644346266031</v>
       </c>
       <c r="C73">
-        <v>-6.051638550704967</v>
+        <v>-6.421050050908553</v>
       </c>
       <c r="D73">
-        <v>11.19266144929503</v>
+        <v>11.09654994909145</v>
       </c>
       <c r="E73">
-        <v>16.6743</v>
+        <v>16.9476</v>
       </c>
       <c r="F73">
-        <v>19.4043</v>
+        <v>19.6776</v>
       </c>
       <c r="G73">
         <v>2.16</v>
@@ -7398,37 +7398,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M73">
-        <v>4.57553394</v>
+        <v>4.639978080000001</v>
       </c>
       <c r="N73">
-        <v>-3.412200606666667</v>
+        <v>-3.476644746666667</v>
       </c>
       <c r="O73">
-        <v>-0.3412200606666667</v>
+        <v>-0.3476644746666668</v>
       </c>
       <c r="P73">
-        <v>-3.070980546</v>
+        <v>-3.128980272000001</v>
       </c>
       <c r="Q73">
-        <v>-3.016980546</v>
+        <v>-3.074980272</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3517346596109358</v>
+        <v>0.3626608974541836</v>
       </c>
       <c r="T73">
-        <v>1.871058293989622</v>
+        <v>1.937881804489251</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.025425083686153</v>
+        <v>0.02507195752384531</v>
       </c>
       <c r="W73">
-        <v>0.2298047652668051</v>
+        <v>0.2298880324158773</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2542508368615299</v>
+        <v>0.250719575238453</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2670644346266031</v>
+        <v>0.268964434626603</v>
       </c>
       <c r="C74">
-        <v>-6.421050050908553</v>
+        <v>-6.788824983433305</v>
       </c>
       <c r="D74">
-        <v>11.09654994909145</v>
+        <v>11.0020750165667</v>
       </c>
       <c r="E74">
-        <v>16.9476</v>
+        <v>17.2209</v>
       </c>
       <c r="F74">
-        <v>19.6776</v>
+        <v>19.9509</v>
       </c>
       <c r="G74">
         <v>2.16</v>
@@ -7480,37 +7480,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M74">
-        <v>4.639978080000001</v>
+        <v>4.704422220000001</v>
       </c>
       <c r="N74">
-        <v>-3.476644746666667</v>
+        <v>-3.541088886666667</v>
       </c>
       <c r="O74">
-        <v>-0.3476644746666668</v>
+        <v>-0.3541088886666668</v>
       </c>
       <c r="P74">
-        <v>-3.128980272000001</v>
+        <v>-3.186979998000001</v>
       </c>
       <c r="Q74">
-        <v>-3.074980272</v>
+        <v>-3.132979998000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3626608974541836</v>
+        <v>0.374396486248783</v>
       </c>
       <c r="T74">
-        <v>1.937881804489251</v>
+        <v>2.00965520465552</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02507195752384531</v>
+        <v>0.02472850605091593</v>
       </c>
       <c r="W74">
-        <v>0.2298880324158773</v>
+        <v>0.229969018273194</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.250719575238453</v>
+        <v>0.2472850605091592</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.268964434626603</v>
+        <v>0.270864434626603</v>
       </c>
       <c r="C75">
-        <v>-6.788824983433305</v>
+        <v>-7.155004796124093</v>
       </c>
       <c r="D75">
-        <v>11.0020750165667</v>
+        <v>10.90919520387591</v>
       </c>
       <c r="E75">
-        <v>17.2209</v>
+        <v>17.4942</v>
       </c>
       <c r="F75">
-        <v>19.9509</v>
+        <v>20.2242</v>
       </c>
       <c r="G75">
         <v>2.16</v>
@@ -7562,37 +7562,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M75">
-        <v>4.704422220000001</v>
+        <v>4.768866360000001</v>
       </c>
       <c r="N75">
-        <v>-3.541088886666667</v>
+        <v>-3.605533026666667</v>
       </c>
       <c r="O75">
-        <v>-0.3541088886666668</v>
+        <v>-0.3605533026666667</v>
       </c>
       <c r="P75">
-        <v>-3.186979998000001</v>
+        <v>-3.244979724000001</v>
       </c>
       <c r="Q75">
-        <v>-3.132979998000001</v>
+        <v>-3.190979724000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.374396486248783</v>
+        <v>0.3870348126429669</v>
       </c>
       <c r="T75">
-        <v>2.00965520465552</v>
+        <v>2.086949635603809</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02472850605091593</v>
+        <v>0.02439433705022787</v>
       </c>
       <c r="W75">
-        <v>0.229969018273194</v>
+        <v>0.2300478153235563</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2472850605091592</v>
+        <v>0.2439433705022787</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.270864434626603</v>
+        <v>0.272764434626603</v>
       </c>
       <c r="C76">
-        <v>-7.155004796124093</v>
+        <v>-7.519629548927171</v>
       </c>
       <c r="D76">
-        <v>10.90919520387591</v>
+        <v>10.81787045107283</v>
       </c>
       <c r="E76">
-        <v>17.4942</v>
+        <v>17.7675</v>
       </c>
       <c r="F76">
-        <v>20.2242</v>
+        <v>20.4975</v>
       </c>
       <c r="G76">
         <v>2.16</v>
@@ -7644,37 +7644,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M76">
-        <v>4.768866360000001</v>
+        <v>4.833310500000001</v>
       </c>
       <c r="N76">
-        <v>-3.605533026666667</v>
+        <v>-3.669977166666667</v>
       </c>
       <c r="O76">
-        <v>-0.3605533026666667</v>
+        <v>-0.3669977166666668</v>
       </c>
       <c r="P76">
-        <v>-3.244979724000001</v>
+        <v>-3.30297945</v>
       </c>
       <c r="Q76">
-        <v>-3.190979724000001</v>
+        <v>-3.24897945</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3870348126429669</v>
+        <v>0.4006842051486856</v>
       </c>
       <c r="T76">
-        <v>2.086949635603809</v>
+        <v>2.170427621027961</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02439433705022787</v>
+        <v>0.0240690792228915</v>
       </c>
       <c r="W76">
-        <v>0.2300478153235563</v>
+        <v>0.2301245111192422</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2439433705022787</v>
+        <v>0.240690792228915</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.272764434626603</v>
+        <v>0.2746644346266031</v>
       </c>
       <c r="C77">
-        <v>-7.519629548927171</v>
+        <v>-7.882737971500877</v>
       </c>
       <c r="D77">
-        <v>10.81787045107283</v>
+        <v>10.72806202849912</v>
       </c>
       <c r="E77">
-        <v>17.7675</v>
+        <v>18.0408</v>
       </c>
       <c r="F77">
-        <v>20.4975</v>
+        <v>20.7708</v>
       </c>
       <c r="G77">
         <v>2.16</v>
@@ -7726,37 +7726,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M77">
-        <v>4.833310500000001</v>
+        <v>4.89775464</v>
       </c>
       <c r="N77">
-        <v>-3.669977166666667</v>
+        <v>-3.734421306666667</v>
       </c>
       <c r="O77">
-        <v>-0.3669977166666668</v>
+        <v>-0.3734421306666668</v>
       </c>
       <c r="P77">
-        <v>-3.30297945</v>
+        <v>-3.360979176000001</v>
       </c>
       <c r="Q77">
-        <v>-3.24897945</v>
+        <v>-3.306979176</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4006842051486856</v>
+        <v>0.4154710470298809</v>
       </c>
       <c r="T77">
-        <v>2.170427621027961</v>
+        <v>2.26086210523746</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0240690792228915</v>
+        <v>0.02375238081206398</v>
       </c>
       <c r="W77">
-        <v>0.2301245111192422</v>
+        <v>0.2301991886045153</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.240690792228915</v>
+        <v>0.2375238081206398</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2746644346266031</v>
+        <v>0.276564434626603</v>
       </c>
       <c r="C78">
-        <v>-7.882737971500877</v>
+        <v>-8.244367517980297</v>
       </c>
       <c r="D78">
-        <v>10.72806202849912</v>
+        <v>10.6397324820197</v>
       </c>
       <c r="E78">
-        <v>18.0408</v>
+        <v>18.3141</v>
       </c>
       <c r="F78">
-        <v>20.7708</v>
+        <v>21.0441</v>
       </c>
       <c r="G78">
         <v>2.16</v>
@@ -7808,37 +7808,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M78">
-        <v>4.89775464</v>
+        <v>4.96219878</v>
       </c>
       <c r="N78">
-        <v>-3.734421306666667</v>
+        <v>-3.798865446666667</v>
       </c>
       <c r="O78">
-        <v>-0.3734421306666668</v>
+        <v>-0.3798865446666668</v>
       </c>
       <c r="P78">
-        <v>-3.360979176000001</v>
+        <v>-3.418978902000001</v>
       </c>
       <c r="Q78">
-        <v>-3.306979176</v>
+        <v>-3.364978902000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4154710470298809</v>
+        <v>0.4315437012485713</v>
       </c>
       <c r="T78">
-        <v>2.26086210523746</v>
+        <v>2.359160457639088</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02375238081206398</v>
+        <v>0.02344390833398523</v>
       </c>
       <c r="W78">
-        <v>0.2301991886045153</v>
+        <v>0.2302719264148463</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2375238081206398</v>
+        <v>0.2344390833398522</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.276564434626603</v>
+        <v>0.2784644346266031</v>
       </c>
       <c r="C79">
-        <v>-8.244367517980297</v>
+        <v>-8.604554419058589</v>
       </c>
       <c r="D79">
-        <v>10.6397324820197</v>
+        <v>10.55284558094141</v>
       </c>
       <c r="E79">
-        <v>18.3141</v>
+        <v>18.5874</v>
       </c>
       <c r="F79">
-        <v>21.0441</v>
+        <v>21.3174</v>
       </c>
       <c r="G79">
         <v>2.16</v>
@@ -7890,37 +7890,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M79">
-        <v>4.96219878</v>
+        <v>5.02664292</v>
       </c>
       <c r="N79">
-        <v>-3.798865446666667</v>
+        <v>-3.863309586666667</v>
       </c>
       <c r="O79">
-        <v>-0.3798865446666668</v>
+        <v>-0.3863309586666668</v>
       </c>
       <c r="P79">
-        <v>-3.418978902000001</v>
+        <v>-3.476978628</v>
       </c>
       <c r="Q79">
-        <v>-3.364978902000001</v>
+        <v>-3.422978628</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4315437012485713</v>
+        <v>0.4490775058507792</v>
       </c>
       <c r="T79">
-        <v>2.359160457639088</v>
+        <v>2.466395023895411</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02344390833398523</v>
+        <v>0.02314334540662644</v>
       </c>
       <c r="W79">
-        <v>0.2302719264148463</v>
+        <v>0.2303427991531175</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2344390833398522</v>
+        <v>0.2314334540662644</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2784644346266031</v>
+        <v>0.2803644346266031</v>
       </c>
       <c r="C80">
-        <v>-8.604554419058589</v>
+        <v>-8.963333731537084</v>
       </c>
       <c r="D80">
-        <v>10.55284558094141</v>
+        <v>10.46736626846292</v>
       </c>
       <c r="E80">
-        <v>18.5874</v>
+        <v>18.8607</v>
       </c>
       <c r="F80">
-        <v>21.3174</v>
+        <v>21.5907</v>
       </c>
       <c r="G80">
         <v>2.16</v>
@@ -7972,37 +7972,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M80">
-        <v>5.02664292</v>
+        <v>5.09108706</v>
       </c>
       <c r="N80">
-        <v>-3.863309586666667</v>
+        <v>-3.927753726666667</v>
       </c>
       <c r="O80">
-        <v>-0.3863309586666668</v>
+        <v>-0.3927753726666667</v>
       </c>
       <c r="P80">
-        <v>-3.476978628</v>
+        <v>-3.534978354000001</v>
       </c>
       <c r="Q80">
-        <v>-3.422978628</v>
+        <v>-3.480978354</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4490775058507792</v>
+        <v>0.4682811966055782</v>
       </c>
       <c r="T80">
-        <v>2.466395023895411</v>
+        <v>2.583842405985669</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02314334540662644</v>
+        <v>0.02285039166730206</v>
       </c>
       <c r="W80">
-        <v>0.2303427991531175</v>
+        <v>0.2304118776448502</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2314334540662644</v>
+        <v>0.2285039166730205</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2803644346266031</v>
+        <v>0.282264434626603</v>
       </c>
       <c r="C81">
-        <v>-8.963333731537084</v>
+        <v>-9.320739385486625</v>
       </c>
       <c r="D81">
-        <v>10.46736626846292</v>
+        <v>10.38326061451338</v>
       </c>
       <c r="E81">
-        <v>18.8607</v>
+        <v>19.134</v>
       </c>
       <c r="F81">
-        <v>21.5907</v>
+        <v>21.864</v>
       </c>
       <c r="G81">
         <v>2.16</v>
@@ -8054,37 +8054,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M81">
-        <v>5.09108706</v>
+        <v>5.155531200000001</v>
       </c>
       <c r="N81">
-        <v>-3.927753726666667</v>
+        <v>-3.992197866666668</v>
       </c>
       <c r="O81">
-        <v>-0.3927753726666667</v>
+        <v>-0.3992197866666669</v>
       </c>
       <c r="P81">
-        <v>-3.534978354000001</v>
+        <v>-3.592978080000001</v>
       </c>
       <c r="Q81">
-        <v>-3.480978354</v>
+        <v>-3.538978080000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4682811966055782</v>
+        <v>0.4894052564358571</v>
       </c>
       <c r="T81">
-        <v>2.583842405985669</v>
+        <v>2.713034526284952</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02285039166730206</v>
+        <v>0.02256476177146078</v>
       </c>
       <c r="W81">
-        <v>0.2304118776448502</v>
+        <v>0.2304792291742895</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2285039166730205</v>
+        <v>0.2256476177146077</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.282264434626603</v>
+        <v>0.284164434626603</v>
       </c>
       <c r="C82">
-        <v>-9.320739385486625</v>
+        <v>-9.676804229153339</v>
       </c>
       <c r="D82">
-        <v>10.38326061451338</v>
+        <v>10.30049577084666</v>
       </c>
       <c r="E82">
-        <v>19.134</v>
+        <v>19.4073</v>
       </c>
       <c r="F82">
-        <v>21.864</v>
+        <v>22.1373</v>
       </c>
       <c r="G82">
         <v>2.16</v>
@@ -8136,37 +8136,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M82">
-        <v>5.155531200000001</v>
+        <v>5.219975340000001</v>
       </c>
       <c r="N82">
-        <v>-3.992197866666668</v>
+        <v>-4.056642006666668</v>
       </c>
       <c r="O82">
-        <v>-0.3992197866666669</v>
+        <v>-0.4056642006666669</v>
       </c>
       <c r="P82">
-        <v>-3.592978080000001</v>
+        <v>-3.650977806000001</v>
       </c>
       <c r="Q82">
-        <v>-3.538978080000001</v>
+        <v>-3.596977806000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4894052564358571</v>
+        <v>0.5127529015114285</v>
       </c>
       <c r="T82">
-        <v>2.713034526284952</v>
+        <v>2.855825817142055</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02256476177146078</v>
+        <v>0.02228618446564028</v>
       </c>
       <c r="W82">
-        <v>0.2304792291742895</v>
+        <v>0.230544917703002</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2256476177146077</v>
+        <v>0.2228618446564027</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.284164434626603</v>
+        <v>0.286064434626603</v>
       </c>
       <c r="C83">
-        <v>-9.676804229153339</v>
+        <v>-10.03156007173372</v>
       </c>
       <c r="D83">
-        <v>10.30049577084666</v>
+        <v>10.21903992826628</v>
       </c>
       <c r="E83">
-        <v>19.4073</v>
+        <v>19.6806</v>
       </c>
       <c r="F83">
-        <v>22.1373</v>
+        <v>22.4106</v>
       </c>
       <c r="G83">
         <v>2.16</v>
@@ -8218,37 +8218,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M83">
-        <v>5.219975340000001</v>
+        <v>5.28441948</v>
       </c>
       <c r="N83">
-        <v>-4.056642006666668</v>
+        <v>-4.121086146666667</v>
       </c>
       <c r="O83">
-        <v>-0.4056642006666669</v>
+        <v>-0.4121086146666668</v>
       </c>
       <c r="P83">
-        <v>-3.650977806000001</v>
+        <v>-3.708977532</v>
       </c>
       <c r="Q83">
-        <v>-3.596977806000001</v>
+        <v>-3.654977532</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5127529015114285</v>
+        <v>0.5386947293731745</v>
       </c>
       <c r="T83">
-        <v>2.855825817142055</v>
+        <v>3.01448280698328</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02228618446564028</v>
+        <v>0.02201440172825442</v>
       </c>
       <c r="W83">
-        <v>0.230544917703002</v>
+        <v>0.2306090040724776</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2228618446564027</v>
+        <v>0.2201440172825442</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.286064434626603</v>
+        <v>0.287964434626603</v>
       </c>
       <c r="C84">
-        <v>-10.03156007173372</v>
+        <v>-10.38503772413608</v>
       </c>
       <c r="D84">
-        <v>10.21903992826628</v>
+        <v>10.13886227586392</v>
       </c>
       <c r="E84">
-        <v>19.6806</v>
+        <v>19.9539</v>
       </c>
       <c r="F84">
-        <v>22.4106</v>
+        <v>22.6839</v>
       </c>
       <c r="G84">
         <v>2.16</v>
@@ -8300,37 +8300,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M84">
-        <v>5.28441948</v>
+        <v>5.348863620000001</v>
       </c>
       <c r="N84">
-        <v>-4.121086146666667</v>
+        <v>-4.185530286666668</v>
       </c>
       <c r="O84">
-        <v>-0.4121086146666668</v>
+        <v>-0.4185530286666668</v>
       </c>
       <c r="P84">
-        <v>-3.708977532</v>
+        <v>-3.766977258000001</v>
       </c>
       <c r="Q84">
-        <v>-3.654977532</v>
+        <v>-3.712977258000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5386947293731745</v>
+        <v>0.5676885369833614</v>
       </c>
       <c r="T84">
-        <v>3.01448280698328</v>
+        <v>3.191805325041121</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02201440172825442</v>
+        <v>0.02174916797249232</v>
       </c>
       <c r="W84">
-        <v>0.2306090040724776</v>
+        <v>0.2306715461920863</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2201440172825442</v>
+        <v>0.2174916797249231</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.287964434626603</v>
+        <v>0.2898644346266031</v>
       </c>
       <c r="C85">
-        <v>-10.38503772413608</v>
+        <v>-10.73726703783807</v>
       </c>
       <c r="D85">
-        <v>10.13886227586392</v>
+        <v>10.05993296216193</v>
       </c>
       <c r="E85">
-        <v>19.9539</v>
+        <v>20.2272</v>
       </c>
       <c r="F85">
-        <v>22.6839</v>
+        <v>22.9572</v>
       </c>
       <c r="G85">
         <v>2.16</v>
@@ -8382,37 +8382,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M85">
-        <v>5.348863620000001</v>
+        <v>5.413307760000001</v>
       </c>
       <c r="N85">
-        <v>-4.185530286666668</v>
+        <v>-4.249974426666668</v>
       </c>
       <c r="O85">
-        <v>-0.4185530286666668</v>
+        <v>-0.4249974426666668</v>
       </c>
       <c r="P85">
-        <v>-3.766977258000001</v>
+        <v>-3.824976984000001</v>
       </c>
       <c r="Q85">
-        <v>-3.712977258000001</v>
+        <v>-3.770976984000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5676885369833614</v>
+        <v>0.6003065705448215</v>
       </c>
       <c r="T85">
-        <v>3.191805325041121</v>
+        <v>3.391293157856191</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02174916797249232</v>
+        <v>0.02149024930615312</v>
       </c>
       <c r="W85">
-        <v>0.2306715461920863</v>
+        <v>0.2307325992136091</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2174916797249231</v>
+        <v>0.2149024930615312</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2898644346266031</v>
+        <v>0.2917644346266031</v>
       </c>
       <c r="C86">
-        <v>-10.73726703783807</v>
+        <v>-11.0882769419432</v>
       </c>
       <c r="D86">
-        <v>10.05993296216193</v>
+        <v>9.982223058056796</v>
       </c>
       <c r="E86">
-        <v>20.2272</v>
+        <v>20.5005</v>
       </c>
       <c r="F86">
-        <v>22.9572</v>
+        <v>23.2305</v>
       </c>
       <c r="G86">
         <v>2.16</v>
@@ -8464,37 +8464,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M86">
-        <v>5.41330776</v>
+        <v>5.4777519</v>
       </c>
       <c r="N86">
-        <v>-4.249974426666667</v>
+        <v>-4.314418566666667</v>
       </c>
       <c r="O86">
-        <v>-0.4249974426666667</v>
+        <v>-0.4314418566666667</v>
       </c>
       <c r="P86">
-        <v>-3.824976984000001</v>
+        <v>-3.88297671</v>
       </c>
       <c r="Q86">
-        <v>-3.770976984000001</v>
+        <v>-3.82897671</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6003065705448211</v>
+        <v>0.6372736752478092</v>
       </c>
       <c r="T86">
-        <v>3.391293157856189</v>
+        <v>3.617379368379935</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02149024930615313</v>
+        <v>0.02123742284372779</v>
       </c>
       <c r="W86">
-        <v>0.2307325992136091</v>
+        <v>0.230792215693449</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2149024930615312</v>
+        <v>0.2123742284372779</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2917644346266031</v>
+        <v>0.293664434626603</v>
       </c>
       <c r="C87">
-        <v>-11.0882769419432</v>
+        <v>-11.43809547853309</v>
       </c>
       <c r="D87">
-        <v>9.982223058056796</v>
+        <v>9.905704521466909</v>
       </c>
       <c r="E87">
-        <v>20.5005</v>
+        <v>20.7738</v>
       </c>
       <c r="F87">
-        <v>23.2305</v>
+        <v>23.5038</v>
       </c>
       <c r="G87">
         <v>2.16</v>
@@ -8546,37 +8546,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M87">
-        <v>5.4777519</v>
+        <v>5.54219604</v>
       </c>
       <c r="N87">
-        <v>-4.314418566666667</v>
+        <v>-4.378862706666667</v>
       </c>
       <c r="O87">
-        <v>-0.4314418566666667</v>
+        <v>-0.4378862706666667</v>
       </c>
       <c r="P87">
-        <v>-3.88297671</v>
+        <v>-3.940976436000001</v>
       </c>
       <c r="Q87">
-        <v>-3.82897671</v>
+        <v>-3.886976436</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6372736752478092</v>
+        <v>0.6795217949083669</v>
       </c>
       <c r="T87">
-        <v>3.617379368379935</v>
+        <v>3.875763608978501</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02123742284372779</v>
+        <v>0.02099047606647515</v>
       </c>
       <c r="W87">
-        <v>0.230792215693449</v>
+        <v>0.2308504457435251</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2123742284372779</v>
+        <v>0.2099047606647514</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.293664434626603</v>
+        <v>0.295564434626603</v>
       </c>
       <c r="C88">
-        <v>-11.43809547853309</v>
+        <v>-11.78674983640604</v>
       </c>
       <c r="D88">
-        <v>9.905704521466909</v>
+        <v>9.830350163593961</v>
       </c>
       <c r="E88">
-        <v>20.7738</v>
+        <v>21.0471</v>
       </c>
       <c r="F88">
-        <v>23.5038</v>
+        <v>23.7771</v>
       </c>
       <c r="G88">
         <v>2.16</v>
@@ -8628,37 +8628,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M88">
-        <v>5.54219604</v>
+        <v>5.60664018</v>
       </c>
       <c r="N88">
-        <v>-4.378862706666667</v>
+        <v>-4.443306846666667</v>
       </c>
       <c r="O88">
-        <v>-0.4378862706666667</v>
+        <v>-0.4443306846666668</v>
       </c>
       <c r="P88">
-        <v>-3.940976436000001</v>
+        <v>-3.998976162</v>
       </c>
       <c r="Q88">
-        <v>-3.886976436</v>
+        <v>-3.944976162000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6795217949083669</v>
+        <v>0.7282696252859338</v>
       </c>
       <c r="T88">
-        <v>3.875763608978501</v>
+        <v>4.173899271207618</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02099047606647515</v>
+        <v>0.02074920622663061</v>
       </c>
       <c r="W88">
-        <v>0.2308504457435251</v>
+        <v>0.2309073371717605</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2099047606647514</v>
+        <v>0.207492062266306</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.295564434626603</v>
+        <v>0.297464434626603</v>
       </c>
       <c r="C89">
-        <v>-11.78674983640604</v>
+        <v>-12.13426638328737</v>
       </c>
       <c r="D89">
-        <v>9.830350163593961</v>
+        <v>9.756133616712631</v>
       </c>
       <c r="E89">
-        <v>21.0471</v>
+        <v>21.3204</v>
       </c>
       <c r="F89">
-        <v>23.7771</v>
+        <v>24.0504</v>
       </c>
       <c r="G89">
         <v>2.16</v>
@@ -8710,37 +8710,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M89">
-        <v>5.60664018</v>
+        <v>5.671084320000001</v>
       </c>
       <c r="N89">
-        <v>-4.443306846666667</v>
+        <v>-4.507750986666668</v>
       </c>
       <c r="O89">
-        <v>-0.4443306846666668</v>
+        <v>-0.4507750986666668</v>
       </c>
       <c r="P89">
-        <v>-3.998976162</v>
+        <v>-4.056975888000001</v>
       </c>
       <c r="Q89">
-        <v>-3.944976162000001</v>
+        <v>-4.002975888000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7282696252859338</v>
+        <v>0.7851420940597617</v>
       </c>
       <c r="T89">
-        <v>4.173899271207618</v>
+        <v>4.52172421047492</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02074920622663061</v>
+        <v>0.02051341979223707</v>
       </c>
       <c r="W89">
-        <v>0.2309073371717605</v>
+        <v>0.2309629356129905</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.207492062266306</v>
+        <v>0.2051341979223706</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.297464434626603</v>
+        <v>0.2993644346266031</v>
       </c>
       <c r="C90">
-        <v>-12.13426638328737</v>
+        <v>-12.48067069659161</v>
       </c>
       <c r="D90">
-        <v>9.756133616712631</v>
+        <v>9.683029303408397</v>
       </c>
       <c r="E90">
-        <v>21.3204</v>
+        <v>21.5937</v>
       </c>
       <c r="F90">
-        <v>24.0504</v>
+        <v>24.3237</v>
       </c>
       <c r="G90">
         <v>2.16</v>
@@ -8792,37 +8792,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M90">
-        <v>5.671084320000001</v>
+        <v>5.735528460000001</v>
       </c>
       <c r="N90">
-        <v>-4.507750986666668</v>
+        <v>-4.572195126666668</v>
       </c>
       <c r="O90">
-        <v>-0.4507750986666668</v>
+        <v>-0.4572195126666668</v>
       </c>
       <c r="P90">
-        <v>-4.056975888000001</v>
+        <v>-4.114975614000001</v>
       </c>
       <c r="Q90">
-        <v>-4.002975888000001</v>
+        <v>-4.060975614000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7851420940597617</v>
+        <v>0.8523550117015583</v>
       </c>
       <c r="T90">
-        <v>4.52172421047492</v>
+        <v>4.932790047790822</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02051341979223707</v>
+        <v>0.02028293192940295</v>
       </c>
       <c r="W90">
-        <v>0.2309629356129905</v>
+        <v>0.2310172846510468</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2051341979223706</v>
+        <v>0.2028293192940295</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2993644346266031</v>
+        <v>0.301264434626603</v>
       </c>
       <c r="C91">
-        <v>-12.48067069659161</v>
+        <v>-12.82598759281188</v>
       </c>
       <c r="D91">
-        <v>9.683029303408397</v>
+        <v>9.61101240718812</v>
       </c>
       <c r="E91">
-        <v>21.5937</v>
+        <v>21.867</v>
       </c>
       <c r="F91">
-        <v>24.3237</v>
+        <v>24.597</v>
       </c>
       <c r="G91">
         <v>2.16</v>
@@ -8874,37 +8874,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M91">
-        <v>5.735528460000001</v>
+        <v>5.7999726</v>
       </c>
       <c r="N91">
-        <v>-4.572195126666668</v>
+        <v>-4.636639266666667</v>
       </c>
       <c r="O91">
-        <v>-0.4572195126666668</v>
+        <v>-0.4636639266666667</v>
       </c>
       <c r="P91">
-        <v>-4.114975614000001</v>
+        <v>-4.172975340000001</v>
       </c>
       <c r="Q91">
-        <v>-4.060975614000001</v>
+        <v>-4.11897534</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8523550117015583</v>
+        <v>0.9330105128717141</v>
       </c>
       <c r="T91">
-        <v>4.932790047790822</v>
+        <v>5.426069052569904</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02028293192940295</v>
+        <v>0.02005756601907625</v>
       </c>
       <c r="W91">
-        <v>0.2310172846510468</v>
+        <v>0.2310704259327018</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2028293192940295</v>
+        <v>0.2005756601907625</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.301264434626603</v>
+        <v>0.303164434626603</v>
       </c>
       <c r="C92">
-        <v>-12.82598759281188</v>
+        <v>-13.17024115560758</v>
       </c>
       <c r="D92">
-        <v>9.61101240718812</v>
+        <v>9.540058844392426</v>
       </c>
       <c r="E92">
-        <v>21.867</v>
+        <v>22.1403</v>
       </c>
       <c r="F92">
-        <v>24.597</v>
+        <v>24.8703</v>
       </c>
       <c r="G92">
         <v>2.16</v>
@@ -8956,37 +8956,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M92">
-        <v>5.7999726</v>
+        <v>5.864416740000001</v>
       </c>
       <c r="N92">
-        <v>-4.636639266666667</v>
+        <v>-4.701083406666668</v>
       </c>
       <c r="O92">
-        <v>-0.4636639266666667</v>
+        <v>-0.4701083406666668</v>
       </c>
       <c r="P92">
-        <v>-4.172975340000001</v>
+        <v>-4.230975066000001</v>
       </c>
       <c r="Q92">
-        <v>-4.11897534</v>
+        <v>-4.176975066000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9330105128717141</v>
+        <v>1.031589458746349</v>
       </c>
       <c r="T92">
-        <v>5.426069052569904</v>
+        <v>6.028965613966561</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02005756601907625</v>
+        <v>0.01983715320567981</v>
       </c>
       <c r="W92">
-        <v>0.2310704259327018</v>
+        <v>0.2311223992741007</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2005756601907625</v>
+        <v>0.198371532056798</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.303164434626603</v>
+        <v>0.3050644346266031</v>
       </c>
       <c r="C93">
-        <v>-13.17024115560758</v>
+        <v>-13.51345476265689</v>
       </c>
       <c r="D93">
-        <v>9.540058844392426</v>
+        <v>9.470145237343113</v>
       </c>
       <c r="E93">
-        <v>22.1403</v>
+        <v>22.4136</v>
       </c>
       <c r="F93">
-        <v>24.8703</v>
+        <v>25.1436</v>
       </c>
       <c r="G93">
         <v>2.16</v>
@@ -9038,37 +9038,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M93">
-        <v>5.864416740000001</v>
+        <v>5.928860880000001</v>
       </c>
       <c r="N93">
-        <v>-4.701083406666668</v>
+        <v>-4.765527546666668</v>
       </c>
       <c r="O93">
-        <v>-0.4701083406666668</v>
+        <v>-0.4765527546666668</v>
       </c>
       <c r="P93">
-        <v>-4.230975066000001</v>
+        <v>-4.288974792000001</v>
       </c>
       <c r="Q93">
-        <v>-4.176975066000001</v>
+        <v>-4.234974792000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.031589458746349</v>
+        <v>1.154813141089643</v>
       </c>
       <c r="T93">
-        <v>6.028965613966561</v>
+        <v>6.782586315712384</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01983715320567981</v>
+        <v>0.01962153197518329</v>
       </c>
       <c r="W93">
-        <v>0.2311223992741007</v>
+        <v>0.2311732427602518</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.198371532056798</v>
+        <v>0.1962153197518328</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3050644346266031</v>
+        <v>0.3069644346266031</v>
       </c>
       <c r="C94">
-        <v>-13.51345476265689</v>
+        <v>-13.85565111133728</v>
       </c>
       <c r="D94">
-        <v>9.470145237343113</v>
+        <v>9.401248888662725</v>
       </c>
       <c r="E94">
-        <v>22.4136</v>
+        <v>22.6869</v>
       </c>
       <c r="F94">
-        <v>25.1436</v>
+        <v>25.4169</v>
       </c>
       <c r="G94">
         <v>2.16</v>
@@ -9120,37 +9120,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M94">
-        <v>5.928860880000001</v>
+        <v>5.993305020000001</v>
       </c>
       <c r="N94">
-        <v>-4.765527546666668</v>
+        <v>-4.829971686666668</v>
       </c>
       <c r="O94">
-        <v>-0.4765527546666668</v>
+        <v>-0.4829971686666668</v>
       </c>
       <c r="P94">
-        <v>-4.288974792000001</v>
+        <v>-4.346974518000001</v>
       </c>
       <c r="Q94">
-        <v>-4.234974792000001</v>
+        <v>-4.292974518000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.154813141089643</v>
+        <v>1.313243589816735</v>
       </c>
       <c r="T94">
-        <v>6.782586315712384</v>
+        <v>7.751527217957009</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01962153197518329</v>
+        <v>0.01941054776039637</v>
       </c>
       <c r="W94">
-        <v>0.2311732427602518</v>
+        <v>0.2312229928380985</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1962153197518328</v>
+        <v>0.1941054776039637</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3069644346266031</v>
+        <v>0.3088644346266031</v>
       </c>
       <c r="C95">
-        <v>-13.85565111133728</v>
+        <v>-14.19685224329308</v>
       </c>
       <c r="D95">
-        <v>9.401248888662725</v>
+        <v>9.333347756706923</v>
       </c>
       <c r="E95">
-        <v>22.6869</v>
+        <v>22.9602</v>
       </c>
       <c r="F95">
-        <v>25.4169</v>
+        <v>25.6902</v>
       </c>
       <c r="G95">
         <v>2.16</v>
@@ -9202,37 +9202,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M95">
-        <v>5.993305020000001</v>
+        <v>6.057749160000001</v>
       </c>
       <c r="N95">
-        <v>-4.829971686666668</v>
+        <v>-4.894415826666668</v>
       </c>
       <c r="O95">
-        <v>-0.4829971686666668</v>
+        <v>-0.4894415826666668</v>
       </c>
       <c r="P95">
-        <v>-4.346974518000001</v>
+        <v>-4.404974244000001</v>
       </c>
       <c r="Q95">
-        <v>-4.292974518000001</v>
+        <v>-4.350974244000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.313243589816735</v>
+        <v>1.524484188119525</v>
       </c>
       <c r="T95">
-        <v>7.751527217957009</v>
+        <v>9.043448420949847</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01941054776039637</v>
+        <v>0.01920405257145598</v>
       </c>
       <c r="W95">
-        <v>0.2312229928380985</v>
+        <v>0.2312716844036507</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1941054776039637</v>
+        <v>0.1920405257145598</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3088644346266031</v>
+        <v>0.3107644346266031</v>
       </c>
       <c r="C96">
-        <v>-14.19685224329308</v>
+        <v>-14.53707956794604</v>
       </c>
       <c r="D96">
-        <v>9.333347756706923</v>
+        <v>9.266420432053961</v>
       </c>
       <c r="E96">
-        <v>22.9602</v>
+        <v>23.2335</v>
       </c>
       <c r="F96">
-        <v>25.6902</v>
+        <v>25.9635</v>
       </c>
       <c r="G96">
         <v>2.16</v>
@@ -9284,37 +9284,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M96">
-        <v>6.057749160000001</v>
+        <v>6.122193300000001</v>
       </c>
       <c r="N96">
-        <v>-4.894415826666668</v>
+        <v>-4.958859966666668</v>
       </c>
       <c r="O96">
-        <v>-0.4894415826666668</v>
+        <v>-0.4958859966666668</v>
       </c>
       <c r="P96">
-        <v>-4.404974244000001</v>
+        <v>-4.462973970000001</v>
       </c>
       <c r="Q96">
-        <v>-4.350974244000001</v>
+        <v>-4.408973970000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.524484188119525</v>
+        <v>1.820221025743431</v>
       </c>
       <c r="T96">
-        <v>9.043448420949847</v>
+        <v>10.85213810513982</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01920405257145598</v>
+        <v>0.01900190464965118</v>
       </c>
       <c r="W96">
-        <v>0.2312716844036507</v>
+        <v>0.2313193508836122</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1920405257145598</v>
+        <v>0.1900190464965118</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3107644346266031</v>
+        <v>0.312664434626603</v>
       </c>
       <c r="C97">
-        <v>-14.53707956794604</v>
+        <v>-14.87635388500158</v>
       </c>
       <c r="D97">
-        <v>9.266420432053961</v>
+        <v>9.200446114998423</v>
       </c>
       <c r="E97">
-        <v>23.2335</v>
+        <v>23.5068</v>
       </c>
       <c r="F97">
-        <v>25.9635</v>
+        <v>26.2368</v>
       </c>
       <c r="G97">
         <v>2.16</v>
@@ -9366,37 +9366,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M97">
-        <v>6.122193300000001</v>
+        <v>6.186637440000001</v>
       </c>
       <c r="N97">
-        <v>-4.958859966666668</v>
+        <v>-5.023304106666668</v>
       </c>
       <c r="O97">
-        <v>-0.4958859966666668</v>
+        <v>-0.5023304106666668</v>
       </c>
       <c r="P97">
-        <v>-4.462973970000001</v>
+        <v>-4.520973696000001</v>
       </c>
       <c r="Q97">
-        <v>-4.408973970000001</v>
+        <v>-4.466973696000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.820221025743431</v>
+        <v>2.263826282179289</v>
       </c>
       <c r="T97">
-        <v>10.85213810513982</v>
+        <v>13.56517263142478</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01900190464965118</v>
+        <v>0.01880396814288398</v>
       </c>
       <c r="W97">
-        <v>0.2313193508836122</v>
+        <v>0.231366024311908</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1900190464965118</v>
+        <v>0.1880396814288398</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.312664434626603</v>
+        <v>0.3145644346266031</v>
       </c>
       <c r="C98">
-        <v>-14.87635388500158</v>
+        <v>-15.21469540600038</v>
       </c>
       <c r="D98">
-        <v>9.200446114998423</v>
+        <v>9.13540459399962</v>
       </c>
       <c r="E98">
-        <v>23.5068</v>
+        <v>23.7801</v>
       </c>
       <c r="F98">
-        <v>26.2368</v>
+        <v>26.5101</v>
       </c>
       <c r="G98">
         <v>2.16</v>
@@ -9448,37 +9448,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M98">
-        <v>6.186637440000001</v>
+        <v>6.25108158</v>
       </c>
       <c r="N98">
-        <v>-5.023304106666668</v>
+        <v>-5.087748246666667</v>
       </c>
       <c r="O98">
-        <v>-0.5023304106666668</v>
+        <v>-0.5087748246666667</v>
       </c>
       <c r="P98">
-        <v>-4.520973696000001</v>
+        <v>-4.578973422000001</v>
       </c>
       <c r="Q98">
-        <v>-4.466973696000001</v>
+        <v>-4.524973422</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.263826282179283</v>
+        <v>3.003168376239044</v>
       </c>
       <c r="T98">
-        <v>13.56517263142475</v>
+        <v>18.08689684189966</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01880396814288398</v>
+        <v>0.01861011280120477</v>
       </c>
       <c r="W98">
-        <v>0.231366024311908</v>
+        <v>0.2314117354014759</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1880396814288398</v>
+        <v>0.1861011280120477</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3145644346266031</v>
+        <v>0.3164644346266031</v>
       </c>
       <c r="C99">
-        <v>-15.21469540600038</v>
+        <v>-15.55212377496228</v>
       </c>
       <c r="D99">
-        <v>9.13540459399962</v>
+        <v>9.071276225037721</v>
       </c>
       <c r="E99">
-        <v>23.7801</v>
+        <v>24.0534</v>
       </c>
       <c r="F99">
-        <v>26.5101</v>
+        <v>26.7834</v>
       </c>
       <c r="G99">
         <v>2.16</v>
@@ -9530,37 +9530,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M99">
-        <v>6.25108158</v>
+        <v>6.31552572</v>
       </c>
       <c r="N99">
-        <v>-5.087748246666667</v>
+        <v>-5.152192386666667</v>
       </c>
       <c r="O99">
-        <v>-0.5087748246666667</v>
+        <v>-0.5152192386666667</v>
       </c>
       <c r="P99">
-        <v>-4.578973422000001</v>
+        <v>-4.636973148</v>
       </c>
       <c r="Q99">
-        <v>-4.524973422</v>
+        <v>-4.582973148</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.003168376239044</v>
+        <v>4.481852564358566</v>
       </c>
       <c r="T99">
-        <v>18.08689684189966</v>
+        <v>27.1303452628495</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01861011280120477</v>
+        <v>0.01842021369098839</v>
       </c>
       <c r="W99">
-        <v>0.2314117354014759</v>
+        <v>0.231456513611665</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1861011280120477</v>
+        <v>0.1842021369098839</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3164644346266031</v>
+        <v>0.318364434626603</v>
       </c>
       <c r="C100">
-        <v>-15.55212377496228</v>
+        <v>-15.88865808816673</v>
       </c>
       <c r="D100">
-        <v>9.071276225037721</v>
+        <v>9.008041911833276</v>
       </c>
       <c r="E100">
-        <v>24.0534</v>
+        <v>24.3267</v>
       </c>
       <c r="F100">
-        <v>26.7834</v>
+        <v>27.0567</v>
       </c>
       <c r="G100">
         <v>2.16</v>
@@ -9612,37 +9612,37 @@
         <v>1.163333333333333</v>
       </c>
       <c r="M100">
-        <v>6.31552572</v>
+        <v>6.379969860000001</v>
       </c>
       <c r="N100">
-        <v>-5.152192386666667</v>
+        <v>-5.216636526666668</v>
       </c>
       <c r="O100">
-        <v>-0.5152192386666667</v>
+        <v>-0.5216636526666668</v>
       </c>
       <c r="P100">
-        <v>-4.636973148</v>
+        <v>-4.694972874000001</v>
       </c>
       <c r="Q100">
-        <v>-4.582973148</v>
+        <v>-4.640972874000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.481852564358566</v>
+        <v>8.917905128717132</v>
       </c>
       <c r="T100">
-        <v>27.1303452628495</v>
+        <v>54.26069052569898</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01842021369098839</v>
+        <v>0.01823415092643295</v>
       </c>
       <c r="W100">
-        <v>0.231456513611665</v>
+        <v>0.2315003872115471</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1842021369098839</v>
+        <v>0.1823415092643295</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.318364434626603</v>
-      </c>
-      <c r="C101">
-        <v>-15.88865808816673</v>
-      </c>
-      <c r="D101">
-        <v>9.008041911833276</v>
-      </c>
-      <c r="E101">
-        <v>24.3267</v>
-      </c>
-      <c r="F101">
-        <v>27.0567</v>
-      </c>
-      <c r="G101">
-        <v>2.16</v>
-      </c>
-      <c r="H101">
-        <v>24.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.217333333333333</v>
-      </c>
-      <c r="K101">
-        <v>0.05400000000000005</v>
-      </c>
-      <c r="L101">
-        <v>1.163333333333333</v>
-      </c>
-      <c r="M101">
-        <v>6.379969860000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.216636526666668</v>
-      </c>
-      <c r="O101">
-        <v>-0.5216636526666668</v>
-      </c>
-      <c r="P101">
-        <v>-4.694972874000001</v>
-      </c>
-      <c r="Q101">
-        <v>-4.640972874000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.917905128717132</v>
-      </c>
-      <c r="T101">
-        <v>54.26069052569898</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01823415092643295</v>
-      </c>
-      <c r="W101">
-        <v>0.2315003872115471</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1823415092643295</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
